--- a/CER.xlsx
+++ b/CER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/ssegura_balanz_com/Documents/Escritorio/curvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3D143A-B813-421E-A1B1-ADA07E814E94}"/>
+  <xr:revisionPtr revIDLastSave="433" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D59E1ED-A355-46FA-B65C-3C1C5E2ADD39}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
@@ -494,13 +494,13 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -45256,7 +45256,7 @@
       </c>
     </row>
     <row r="2613" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2613" s="48">
+      <c r="A2613" s="46">
         <v>46096</v>
       </c>
       <c r="B2613" s="39">
@@ -45816,7 +45816,7 @@
       </c>
       <c r="D2645" s="35">
         <f>+D2644*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>746.16345487102365</v>
+        <v>746.28449711707299</v>
       </c>
       <c r="E2645" s="35">
         <f>+E2644*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45837,7 +45837,7 @@
       </c>
       <c r="D2646" s="35">
         <f>+D2645*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>746.77786519694644</v>
+        <v>747.02016867926784</v>
       </c>
       <c r="E2646" s="35">
         <f>+E2645*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45858,7 +45858,7 @@
       </c>
       <c r="D2647" s="35">
         <f>+D2646*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>747.3927814442543</v>
+        <v>747.75656545101674</v>
       </c>
       <c r="E2647" s="35">
         <f>+E2646*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45880,7 +45880,7 @@
       </c>
       <c r="D2648" s="35">
         <f>+D2647*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>748.00820402953605</v>
+        <v>748.49368814721618</v>
       </c>
       <c r="E2648" s="35">
         <f>+E2647*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45902,7 +45902,7 @@
       </c>
       <c r="D2649" s="35">
         <f>+D2648*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>748.62413336972349</v>
+        <v>749.23153748346715</v>
       </c>
       <c r="E2649" s="35">
         <f>+E2648*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45923,7 +45923,7 @@
       </c>
       <c r="D2650" s="35">
         <f>+D2649*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>749.24056988209168</v>
+        <v>749.97011417607609</v>
       </c>
       <c r="E2650" s="35">
         <f>+E2649*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45945,7 +45945,7 @@
       </c>
       <c r="D2651" s="35">
         <f>+D2650*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>749.85751398425941</v>
+        <v>750.70941894205566</v>
       </c>
       <c r="E2651" s="35">
         <f>+E2650*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45966,7 +45966,7 @@
       </c>
       <c r="D2652" s="35">
         <f>+D2651*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>750.47496609418931</v>
+        <v>751.4494524991253</v>
       </c>
       <c r="E2652" s="35">
         <f>+E2651*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45988,7 +45988,7 @@
       </c>
       <c r="D2653" s="35">
         <f>+D2652*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>751.09292663018812</v>
+        <v>752.19021556571192</v>
       </c>
       <c r="E2653" s="35">
         <f>+E2652*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="D2654" s="35">
         <f>+D2653*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>751.71139601090692</v>
+        <v>752.93170886095061</v>
       </c>
       <c r="E2654" s="35">
         <f>+E2653*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46030,7 +46030,7 @@
       </c>
       <c r="D2655" s="35">
         <f>+D2654*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>752.33037465534176</v>
+        <v>753.67393310468537</v>
       </c>
       <c r="E2655" s="35">
         <f>+E2654*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46051,7 +46051,7 @@
       </c>
       <c r="D2656" s="35">
         <f>+D2655*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>752.94986298283357</v>
+        <v>754.41688901747</v>
       </c>
       <c r="E2656" s="35">
         <f>+E2655*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46072,7 +46072,7 @@
       </c>
       <c r="D2657" s="35">
         <f>+D2656*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>753.56986141306857</v>
+        <v>755.16057732056834</v>
       </c>
       <c r="E2657" s="35">
         <f>+E2656*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46093,7 +46093,7 @@
       </c>
       <c r="D2658" s="35">
         <f>+D2657*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>754.19037036607858</v>
+        <v>755.90499873595547</v>
       </c>
       <c r="E2658" s="35">
         <f>+E2657*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46114,7 +46114,7 @@
       </c>
       <c r="D2659" s="35">
         <f>+D2658*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>754.81139026224128</v>
+        <v>756.65015398631795</v>
       </c>
       <c r="E2659" s="35">
         <f>+E2658*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46135,7 +46135,7 @@
       </c>
       <c r="D2660" s="35">
         <f>+D2659*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>755.43292152228048</v>
+        <v>757.39604379505499</v>
       </c>
       <c r="E2660" s="35">
         <f>+E2659*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46156,7 +46156,7 @@
       </c>
       <c r="D2661" s="35">
         <f>+D2660*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>756.05496456726655</v>
+        <v>758.14266888627867</v>
       </c>
       <c r="E2661" s="35">
         <f>+E2660*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46177,7 +46177,7 @@
       </c>
       <c r="D2662" s="35">
         <f>+D2661*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>756.67751981861636</v>
+        <v>758.8900299848151</v>
       </c>
       <c r="E2662" s="35">
         <f>+E2661*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46198,7 +46198,7 @@
       </c>
       <c r="D2663" s="35">
         <f>+D2662*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>757.30058769809398</v>
+        <v>759.6381278162047</v>
       </c>
       <c r="E2663" s="35">
         <f>+E2662*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46220,7 +46220,7 @@
       </c>
       <c r="D2664" s="35">
         <f>+D2663*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>757.92416862781067</v>
+        <v>760.38696310670332</v>
       </c>
       <c r="E2664" s="35">
         <f>+E2663*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46241,7 +46241,7 @@
       </c>
       <c r="D2665" s="35">
         <f>+D2664*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>758.54826303022526</v>
+        <v>761.13653658328258</v>
       </c>
       <c r="E2665" s="35">
         <f>+E2664*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46262,7 +46262,7 @@
       </c>
       <c r="D2666" s="35">
         <f>+D2665*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>759.17287132814454</v>
+        <v>761.88684897363089</v>
       </c>
       <c r="E2666" s="35">
         <f>+E2665*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46283,7 +46283,7 @@
       </c>
       <c r="D2667" s="35">
         <f>+D2666*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>759.79799394472332</v>
+        <v>762.63790100615381</v>
       </c>
       <c r="E2667" s="35">
         <f>+E2666*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46304,7 +46304,7 @@
       </c>
       <c r="D2668" s="35">
         <f>+D2667*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>760.42363130346496</v>
+        <v>763.38969340997505</v>
       </c>
       <c r="E2668" s="35">
         <f>+E2667*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46325,7 +46325,7 @@
       </c>
       <c r="D2669" s="35">
         <f>+D2668*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>761.04978382822151</v>
+        <v>764.14222691493705</v>
       </c>
       <c r="E2669" s="35">
         <f>+E2668*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46346,7 +46346,7 @@
       </c>
       <c r="D2670" s="35">
         <f>+D2669*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>761.67645194319391</v>
+        <v>764.89550225160178</v>
       </c>
       <c r="E2670" s="35">
         <f>+E2669*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46367,7 +46367,7 @@
       </c>
       <c r="D2671" s="35">
         <f>+D2670*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>762.30363607293259</v>
+        <v>765.64952015125129</v>
       </c>
       <c r="E2671" s="35">
         <f>+E2670*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46388,7 +46388,7 @@
       </c>
       <c r="D2672" s="35">
         <f>+D2671*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>762.93133664233744</v>
+        <v>766.40428134588853</v>
       </c>
       <c r="E2672" s="35">
         <f>+E2671*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46409,7 +46409,7 @@
       </c>
       <c r="D2673" s="35">
         <f>+D2672*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>763.5595540766584</v>
+        <v>767.15978656823813</v>
       </c>
       <c r="E2673" s="35">
         <f>+E2672*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46430,7 +46430,7 @@
       </c>
       <c r="D2674" s="35">
         <f>+D2673*((1+INFLA!$C$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>764.18828880149533</v>
+        <v>767.91603655174697</v>
       </c>
       <c r="E2674" s="35">
         <f>+E2673*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="D2675" s="35">
         <f>+D2674*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>764.74281913951279</v>
+        <v>768.47327191580348</v>
       </c>
       <c r="E2675" s="35">
         <f>+E2674*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46472,7 +46472,7 @@
       </c>
       <c r="D2676" s="35">
         <f>+D2675*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>765.29775187037012</v>
+        <v>769.03091163559179</v>
       </c>
       <c r="E2676" s="35">
         <f>+E2675*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46493,7 +46493,7 @@
       </c>
       <c r="D2677" s="35">
         <f>+D2676*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>765.8530872860623</v>
+        <v>769.58895600453116</v>
       </c>
       <c r="E2677" s="35">
         <f>+E2676*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46514,7 +46514,7 @@
       </c>
       <c r="D2678" s="35">
         <f>+D2677*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>766.40882567879589</v>
+        <v>770.14740531625375</v>
       </c>
       <c r="E2678" s="35">
         <f>+E2677*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46535,7 +46535,7 @@
       </c>
       <c r="D2679" s="35">
         <f>+D2678*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>766.9649673409898</v>
+        <v>770.7062598646047</v>
       </c>
       <c r="E2679" s="35">
         <f>+E2678*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46556,7 +46556,7 @@
       </c>
       <c r="D2680" s="35">
         <f>+D2679*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>767.52151256527497</v>
+        <v>771.2655199436424</v>
       </c>
       <c r="E2680" s="35">
         <f>+E2679*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46577,7 +46577,7 @@
       </c>
       <c r="D2681" s="35">
         <f>+D2680*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>768.07846164449461</v>
+        <v>771.82518584763875</v>
       </c>
       <c r="E2681" s="35">
         <f>+E2680*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46598,7 +46598,7 @@
       </c>
       <c r="D2682" s="35">
         <f>+D2681*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>768.63581487170461</v>
+        <v>772.38525787107903</v>
       </c>
       <c r="E2682" s="35">
         <f>+E2681*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46619,7 +46619,7 @@
       </c>
       <c r="D2683" s="35">
         <f>+D2682*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>769.19357254017336</v>
+        <v>772.94573630866228</v>
       </c>
       <c r="E2683" s="35">
         <f>+E2682*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46640,7 +46640,7 @@
       </c>
       <c r="D2684" s="35">
         <f>+D2683*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>769.75173494338219</v>
+        <v>773.50662145530146</v>
       </c>
       <c r="E2684" s="35">
         <f>+E2683*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46661,7 +46661,7 @@
       </c>
       <c r="D2685" s="35">
         <f>+D2684*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>770.31030237502534</v>
+        <v>774.0679136061234</v>
       </c>
       <c r="E2685" s="35">
         <f>+E2684*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46682,7 +46682,7 @@
       </c>
       <c r="D2686" s="35">
         <f>+D2685*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>770.86927512901013</v>
+        <v>774.62961305646911</v>
       </c>
       <c r="E2686" s="35">
         <f>+E2685*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46703,7 +46703,7 @@
       </c>
       <c r="D2687" s="35">
         <f>+D2686*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>771.42865349945725</v>
+        <v>775.19172010189402</v>
       </c>
       <c r="E2687" s="35">
         <f>+E2686*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46724,7 +46724,7 @@
       </c>
       <c r="D2688" s="35">
         <f>+D2687*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>771.98843778070068</v>
+        <v>775.75423503816785</v>
       </c>
       <c r="E2688" s="35">
         <f>+E2687*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46745,7 +46745,7 @@
       </c>
       <c r="D2689" s="35">
         <f>+D2688*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>772.548628267288</v>
+        <v>776.31715816127519</v>
       </c>
       <c r="E2689" s="35">
         <f>+E2688*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46766,7 +46766,7 @@
       </c>
       <c r="D2690" s="35">
         <f>+D2689*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>773.10922525398064</v>
+        <v>776.88048976741516</v>
       </c>
       <c r="E2690" s="35">
         <f>+E2689*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46787,7 +46787,7 @@
       </c>
       <c r="D2691" s="35">
         <f>+D2690*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>773.67022903575389</v>
+        <v>777.44423015300197</v>
       </c>
       <c r="E2691" s="35">
         <f>+E2690*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46808,7 +46808,7 @@
       </c>
       <c r="D2692" s="35">
         <f>+D2691*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>774.23163990779699</v>
+        <v>778.00837961466482</v>
       </c>
       <c r="E2692" s="35">
         <f>+E2691*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46829,7 +46829,7 @@
       </c>
       <c r="D2693" s="35">
         <f>+D2692*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>774.79345816551358</v>
+        <v>778.57293844924823</v>
       </c>
       <c r="E2693" s="35">
         <f>+E2692*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46850,7 +46850,7 @@
       </c>
       <c r="D2694" s="35">
         <f>+D2693*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>775.3556841045214</v>
+        <v>779.13790695381215</v>
       </c>
       <c r="E2694" s="35">
         <f>+E2693*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="D2695" s="35">
         <f>+D2694*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>775.91831802065292</v>
+        <v>779.70328542563209</v>
       </c>
       <c r="E2695" s="35">
         <f>+E2694*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46892,7 +46892,7 @@
       </c>
       <c r="D2696" s="35">
         <f>+D2695*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>776.48136020995514</v>
+        <v>780.26907416219922</v>
       </c>
       <c r="E2696" s="35">
         <f>+E2695*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46913,7 +46913,7 @@
       </c>
       <c r="D2697" s="35">
         <f>+D2696*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>777.04481096868994</v>
+        <v>780.83527346122048</v>
       </c>
       <c r="E2697" s="35">
         <f>+E2696*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46934,7 +46934,7 @@
       </c>
       <c r="D2698" s="35">
         <f>+D2697*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>777.60867059333418</v>
+        <v>781.40188362061906</v>
       </c>
       <c r="E2698" s="35">
         <f>+E2697*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46955,7 +46955,7 @@
       </c>
       <c r="D2699" s="35">
         <f>+D2698*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>778.17293938057992</v>
+        <v>781.96890493853425</v>
       </c>
       <c r="E2699" s="35">
         <f>+E2698*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46976,7 +46976,7 @@
       </c>
       <c r="D2700" s="35">
         <f>+D2699*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>778.73761762733432</v>
+        <v>782.5363377133217</v>
       </c>
       <c r="E2700" s="35">
         <f>+E2699*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46997,7 +46997,7 @@
       </c>
       <c r="D2701" s="35">
         <f>+D2700*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>779.3027056307202</v>
+        <v>783.1041822435534</v>
       </c>
       <c r="E2701" s="35">
         <f>+E2700*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47018,7 +47018,7 @@
       </c>
       <c r="D2702" s="35">
         <f>+D2701*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>779.86820368807594</v>
+        <v>783.67243882801824</v>
       </c>
       <c r="E2702" s="35">
         <f>+E2701*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47039,7 +47039,7 @@
       </c>
       <c r="D2703" s="35">
         <f>+D2702*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>780.43411209695569</v>
+        <v>784.24110776572172</v>
       </c>
       <c r="E2703" s="35">
         <f>+E2702*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="D2704" s="35">
         <f>+D2703*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>781.00043115512938</v>
+        <v>784.81018935588656</v>
       </c>
       <c r="E2704" s="35">
         <f>+E2703*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47081,7 +47081,7 @@
       </c>
       <c r="D2705" s="35">
         <f>+D2704*((1+INFLA!$C$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>781.56716116058317</v>
+        <v>785.3796838979523</v>
       </c>
       <c r="E2705" s="35">
         <f>+E2704*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47102,7 +47102,7 @@
       </c>
       <c r="D2706" s="35">
         <f>+D2705*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>782.057663847507</v>
+        <v>785.87257928090992</v>
       </c>
       <c r="E2706" s="35">
         <f>+E2705*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47123,7 +47123,7 @@
       </c>
       <c r="D2707" s="35">
         <f>+D2706*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>782.5484743683545</v>
+        <v>786.36578399942016</v>
       </c>
       <c r="E2707" s="35">
         <f>+E2706*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47144,7 +47144,7 @@
       </c>
       <c r="D2708" s="35">
         <f>+D2707*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>783.03959291631884</v>
+        <v>786.85929824761854</v>
       </c>
       <c r="E2708" s="35">
         <f>+E2707*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47165,7 +47165,7 @@
       </c>
       <c r="D2709" s="35">
         <f>+D2708*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>783.53101968471435</v>
+        <v>787.35312221976233</v>
       </c>
       <c r="E2709" s="35">
         <f>+E2708*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47186,7 +47186,7 @@
       </c>
       <c r="D2710" s="35">
         <f>+D2709*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>784.0227548669767</v>
+        <v>787.84725611023077</v>
       </c>
       <c r="E2710" s="35">
         <f>+E2709*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47207,7 +47207,7 @@
       </c>
       <c r="D2711" s="35">
         <f>+D2710*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>784.51479865666283</v>
+        <v>788.34170011352512</v>
       </c>
       <c r="E2711" s="35">
         <f>+E2710*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47228,7 +47228,7 @@
       </c>
       <c r="D2712" s="35">
         <f>+D2711*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>785.00715124745125</v>
+        <v>788.83645442426871</v>
       </c>
       <c r="E2712" s="35">
         <f>+E2711*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47249,7 +47249,7 @@
       </c>
       <c r="D2713" s="35">
         <f>+D2712*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>785.49981283314219</v>
+        <v>789.33151923720686</v>
       </c>
       <c r="E2713" s="35">
         <f>+E2712*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="D2714" s="35">
         <f>+D2713*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>785.9927836076572</v>
+        <v>789.82689474720735</v>
       </c>
       <c r="E2714" s="35">
         <f>+E2713*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47291,7 +47291,7 @@
       </c>
       <c r="D2715" s="35">
         <f>+D2714*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>786.48606376503972</v>
+        <v>790.32258114926003</v>
       </c>
       <c r="E2715" s="35">
         <f>+E2714*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47312,7 +47312,7 @@
       </c>
       <c r="D2716" s="35">
         <f>+D2715*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>786.97965349945491</v>
+        <v>790.81857863847722</v>
       </c>
       <c r="E2716" s="35">
         <f>+E2715*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47333,7 +47333,7 @@
       </c>
       <c r="D2717" s="35">
         <f>+D2716*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>787.47355300518984</v>
+        <v>791.31488741009377</v>
       </c>
       <c r="E2717" s="35">
         <f>+E2716*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47354,7 +47354,7 @@
       </c>
       <c r="D2718" s="35">
         <f>+D2717*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>787.96776247665343</v>
+        <v>791.811507659467</v>
       </c>
       <c r="E2718" s="35">
         <f>+E2717*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47375,7 +47375,7 @@
       </c>
       <c r="D2719" s="35">
         <f>+D2718*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>788.46228210837671</v>
+        <v>792.30843958207674</v>
       </c>
       <c r="E2719" s="35">
         <f>+E2718*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47396,7 +47396,7 @@
       </c>
       <c r="D2720" s="35">
         <f>+D2719*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>788.95711209501269</v>
+        <v>792.80568337352565</v>
       </c>
       <c r="E2720" s="35">
         <f>+E2719*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47417,7 +47417,7 @@
       </c>
       <c r="D2721" s="35">
         <f>+D2720*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>789.45225263133671</v>
+        <v>793.30323922953903</v>
       </c>
       <c r="E2721" s="35">
         <f>+E2720*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47438,7 +47438,7 @@
       </c>
       <c r="D2722" s="35">
         <f>+D2721*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>789.94770391224608</v>
+        <v>793.80110734596508</v>
       </c>
       <c r="E2722" s="35">
         <f>+E2721*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="D2723" s="35">
         <f>+D2722*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>790.4434661327607</v>
+        <v>794.29928791877489</v>
       </c>
       <c r="E2723" s="35">
         <f>+E2722*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47480,7 +47480,7 @@
       </c>
       <c r="D2724" s="35">
         <f>+D2723*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>790.93953948802266</v>
+        <v>794.79778114406258</v>
       </c>
       <c r="E2724" s="35">
         <f>+E2723*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47501,7 +47501,7 @@
       </c>
       <c r="D2725" s="35">
         <f>+D2724*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>791.4359241732966</v>
+        <v>795.29658721804526</v>
       </c>
       <c r="E2725" s="35">
         <f>+E2724*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47522,7 +47522,7 @@
       </c>
       <c r="D2726" s="35">
         <f>+D2725*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>791.93262038396972</v>
+        <v>795.79570633706317</v>
       </c>
       <c r="E2726" s="35">
         <f>+E2725*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47543,7 +47543,7 @@
       </c>
       <c r="D2727" s="35">
         <f>+D2726*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>792.42962831555189</v>
+        <v>796.29513869757989</v>
       </c>
       <c r="E2727" s="35">
         <f>+E2726*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47564,7 +47564,7 @@
       </c>
       <c r="D2728" s="35">
         <f>+D2727*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>792.92694816367555</v>
+        <v>796.79488449618225</v>
       </c>
       <c r="E2728" s="35">
         <f>+E2727*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47585,7 +47585,7 @@
       </c>
       <c r="D2729" s="35">
         <f>+D2728*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>793.424580124096</v>
+        <v>797.29494392958031</v>
       </c>
       <c r="E2729" s="35">
         <f>+E2728*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47606,7 +47606,7 @@
       </c>
       <c r="D2730" s="35">
         <f>+D2729*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>793.92252439269134</v>
+        <v>797.79531719460783</v>
       </c>
       <c r="E2730" s="35">
         <f>+E2729*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47627,7 +47627,7 @@
       </c>
       <c r="D2731" s="35">
         <f>+D2730*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>794.4207811654627</v>
+        <v>798.29600448822202</v>
       </c>
       <c r="E2731" s="35">
         <f>+E2730*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47648,7 +47648,7 @@
       </c>
       <c r="D2732" s="35">
         <f>+D2731*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>794.91935063853418</v>
+        <v>798.79700600750357</v>
       </c>
       <c r="E2732" s="35">
         <f>+E2731*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47669,7 +47669,7 @@
       </c>
       <c r="D2733" s="35">
         <f>+D2732*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>795.41823300815292</v>
+        <v>799.29832194965695</v>
       </c>
       <c r="E2733" s="35">
         <f>+E2732*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47690,7 +47690,7 @@
       </c>
       <c r="D2734" s="35">
         <f>+D2733*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>795.91742847068917</v>
+        <v>799.79995251201046</v>
       </c>
       <c r="E2734" s="35">
         <f>+E2733*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47711,7 +47711,7 @@
       </c>
       <c r="D2735" s="35">
         <f>+D2734*((1+INFLA!$C$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>796.41693722263653</v>
+        <v>800.30189789201609</v>
       </c>
       <c r="E2735" s="35">
         <f>+E2734*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47728,7 +47728,7 @@
       </c>
       <c r="D2736" s="35">
         <f>+D2735*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>796.89067849897128</v>
+        <v>800.77795010140619</v>
       </c>
       <c r="E2736" s="35">
         <f>+E2735*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="D2737" s="35">
         <f>+D2736*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>797.36470157593885</v>
+        <v>801.25428548606635</v>
       </c>
       <c r="E2737" s="35">
         <f>+E2736*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47762,7 +47762,7 @@
       </c>
       <c r="D2738" s="35">
         <f>+D2737*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>797.83900662116582</v>
+        <v>801.73090421444067</v>
       </c>
       <c r="E2738" s="35">
         <f>+E2737*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47779,7 +47779,7 @@
       </c>
       <c r="D2739" s="35">
         <f>+D2738*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>798.31359380237825</v>
+        <v>802.20780645507375</v>
       </c>
       <c r="E2739" s="35">
         <f>+E2738*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47796,7 +47796,7 @@
       </c>
       <c r="D2740" s="35">
         <f>+D2739*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>798.78846328740224</v>
+        <v>802.68499237661013</v>
       </c>
       <c r="E2740" s="35">
         <f>+E2739*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47813,7 +47813,7 @@
       </c>
       <c r="D2741" s="35">
         <f>+D2740*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>799.26361524416359</v>
+        <v>803.16246214779471</v>
       </c>
       <c r="E2741" s="35">
         <f>+E2740*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47830,7 +47830,7 @@
       </c>
       <c r="D2742" s="35">
         <f>+D2741*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>799.73904984068804</v>
+        <v>803.64021593747293</v>
       </c>
       <c r="E2742" s="35">
         <f>+E2741*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47847,7 +47847,7 @@
       </c>
       <c r="D2743" s="35">
         <f>+D2742*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>800.21476724510126</v>
+        <v>804.11825391459058</v>
       </c>
       <c r="E2743" s="35">
         <f>+E2742*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47864,7 +47864,7 @@
       </c>
       <c r="D2744" s="35">
         <f>+D2743*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>800.69076762562884</v>
+        <v>804.59657624819397</v>
       </c>
       <c r="E2744" s="35">
         <f>+E2743*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47881,7 +47881,7 @@
       </c>
       <c r="D2745" s="35">
         <f>+D2744*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>801.16705115059665</v>
+        <v>805.07518310742989</v>
       </c>
       <c r="E2745" s="35">
         <f>+E2744*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47898,7 +47898,7 @@
       </c>
       <c r="D2746" s="35">
         <f>+D2745*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>801.64361798843038</v>
+        <v>805.55407466154577</v>
       </c>
       <c r="E2746" s="35">
         <f>+E2745*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47915,7 +47915,7 @@
       </c>
       <c r="D2747" s="35">
         <f>+D2746*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>802.12046830765621</v>
+        <v>806.03325107988974</v>
       </c>
       <c r="E2747" s="35">
         <f>+E2746*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47932,7 +47932,7 @@
       </c>
       <c r="D2748" s="35">
         <f>+D2747*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>802.59760227690037</v>
+        <v>806.51271253191067</v>
       </c>
       <c r="E2748" s="35">
         <f>+E2747*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47949,7 +47949,7 @@
       </c>
       <c r="D2749" s="35">
         <f>+D2748*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>803.07502006488949</v>
+        <v>806.99245918715826</v>
       </c>
       <c r="E2749" s="35">
         <f>+E2748*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47966,7 +47966,7 @@
       </c>
       <c r="D2750" s="35">
         <f>+D2749*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>803.55272184045043</v>
+        <v>807.47249121528296</v>
       </c>
       <c r="E2750" s="35">
         <f>+E2749*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -47983,7 +47983,7 @@
       </c>
       <c r="D2751" s="35">
         <f>+D2750*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>804.03070777251071</v>
+        <v>807.95280878603626</v>
       </c>
       <c r="E2751" s="35">
         <f>+E2750*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48000,7 +48000,7 @@
       </c>
       <c r="D2752" s="35">
         <f>+D2751*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>804.50897803009821</v>
+        <v>808.4334120692705</v>
       </c>
       <c r="E2752" s="35">
         <f>+E2751*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48017,7 +48017,7 @@
       </c>
       <c r="D2753" s="35">
         <f>+D2752*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>804.9875327823413</v>
+        <v>808.9143012349391</v>
       </c>
       <c r="E2753" s="35">
         <f>+E2752*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48034,7 +48034,7 @@
       </c>
       <c r="D2754" s="35">
         <f>+D2753*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>805.466372198469</v>
+        <v>809.39547645309665</v>
       </c>
       <c r="E2754" s="35">
         <f>+E2753*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48051,7 +48051,7 @@
       </c>
       <c r="D2755" s="35">
         <f>+D2754*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>805.94549644781102</v>
+        <v>809.8769378938988</v>
       </c>
       <c r="E2755" s="35">
         <f>+E2754*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48068,7 +48068,7 @@
       </c>
       <c r="D2756" s="35">
         <f>+D2755*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>806.4249056997977</v>
+        <v>810.35868572760251</v>
       </c>
       <c r="E2756" s="35">
         <f>+E2755*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48085,7 +48085,7 @@
       </c>
       <c r="D2757" s="35">
         <f>+D2756*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>806.90460012396034</v>
+        <v>810.84072012456591</v>
       </c>
       <c r="E2757" s="35">
         <f>+E2756*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48102,7 +48102,7 @@
       </c>
       <c r="D2758" s="35">
         <f>+D2757*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>807.38457988993093</v>
+        <v>811.32304125524854</v>
       </c>
       <c r="E2758" s="35">
         <f>+E2757*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48119,7 +48119,7 @@
       </c>
       <c r="D2759" s="35">
         <f>+D2758*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>807.86484516744235</v>
+        <v>811.80564929021125</v>
       </c>
       <c r="E2759" s="35">
         <f>+E2758*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48136,7 +48136,7 @@
       </c>
       <c r="D2760" s="35">
         <f>+D2759*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>808.34539612632864</v>
+        <v>812.28854440011651</v>
       </c>
       <c r="E2760" s="35">
         <f>+E2759*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="D2761" s="35">
         <f>+D2760*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>808.82623293652466</v>
+        <v>812.77172675572808</v>
       </c>
       <c r="E2761" s="35">
         <f>+E2760*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48170,7 +48170,7 @@
       </c>
       <c r="D2762" s="35">
         <f>+D2761*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>809.30735576806649</v>
+        <v>813.25519652791149</v>
       </c>
       <c r="E2762" s="35">
         <f>+E2761*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48187,7 +48187,7 @@
       </c>
       <c r="D2763" s="35">
         <f>+D2762*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>809.78876479109124</v>
+        <v>813.7389538876339</v>
       </c>
       <c r="E2763" s="35">
         <f>+E2762*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48204,7 +48204,7 @@
       </c>
       <c r="D2764" s="35">
         <f>+D2763*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>810.27046017583723</v>
+        <v>814.22299900596397</v>
       </c>
       <c r="E2764" s="35">
         <f>+E2763*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48221,7 +48221,7 @@
       </c>
       <c r="D2765" s="35">
         <f>+D2764*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>810.75244209264417</v>
+        <v>814.70733205407237</v>
       </c>
       <c r="E2765" s="35">
         <f>+E2764*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48238,7 +48238,7 @@
       </c>
       <c r="D2766" s="35">
         <f>+D2765*((1+INFLA!$C$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
-        <v>811.23471071195297</v>
+        <v>815.19195320323149</v>
       </c>
       <c r="E2766" s="35">
         <f>+E2765*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -48255,7 +48255,7 @@
       </c>
       <c r="D2767" s="35">
         <f>+D2766*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>811.67596223660007</v>
+        <v>815.63535717434024</v>
       </c>
       <c r="E2767" s="35">
         <f>+E2766*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48272,7 +48272,7 @@
       </c>
       <c r="D2768" s="35">
         <f>+D2767*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>812.11745376935505</v>
+        <v>816.07900232432826</v>
       </c>
       <c r="E2768" s="35">
         <f>+E2767*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48289,7 +48289,7 @@
       </c>
       <c r="D2769" s="35">
         <f>+D2768*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>812.55918544076462</v>
+        <v>816.52288878437889</v>
       </c>
       <c r="E2769" s="35">
         <f>+E2768*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48306,7 +48306,7 @@
       </c>
       <c r="D2770" s="35">
         <f>+D2769*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>813.00115738144632</v>
+        <v>816.9670166857469</v>
       </c>
       <c r="E2770" s="35">
         <f>+E2769*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="D2771" s="35">
         <f>+D2770*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>813.44336972208885</v>
+        <v>817.41138615975842</v>
       </c>
       <c r="E2771" s="35">
         <f>+E2770*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48340,7 +48340,7 @@
       </c>
       <c r="D2772" s="35">
         <f>+D2771*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>813.88582259345196</v>
+        <v>817.85599733781112</v>
       </c>
       <c r="E2772" s="35">
         <f>+E2771*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48357,7 +48357,7 @@
       </c>
       <c r="D2773" s="35">
         <f>+D2772*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>814.32851612636659</v>
+        <v>818.30085035137404</v>
       </c>
       <c r="E2773" s="35">
         <f>+E2772*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48374,7 +48374,7 @@
       </c>
       <c r="D2774" s="35">
         <f>+D2773*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>814.77145045173461</v>
+        <v>818.74594533198785</v>
       </c>
       <c r="E2774" s="35">
         <f>+E2773*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48391,7 +48391,7 @@
       </c>
       <c r="D2775" s="35">
         <f>+D2774*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>815.21462570052938</v>
+        <v>819.19128241126452</v>
       </c>
       <c r="E2775" s="35">
         <f>+E2774*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48408,7 +48408,7 @@
       </c>
       <c r="D2776" s="35">
         <f>+D2775*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>815.65804200379534</v>
+        <v>819.63686172088796</v>
       </c>
       <c r="E2776" s="35">
         <f>+E2775*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48425,7 +48425,7 @@
       </c>
       <c r="D2777" s="35">
         <f>+D2776*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>816.10169949264832</v>
+        <v>820.08268339261338</v>
       </c>
       <c r="E2777" s="35">
         <f>+E2776*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48442,7 +48442,7 @@
       </c>
       <c r="D2778" s="35">
         <f>+D2777*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>816.54559829827531</v>
+        <v>820.52874755826781</v>
       </c>
       <c r="E2778" s="35">
         <f>+E2777*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48459,7 +48459,7 @@
       </c>
       <c r="D2779" s="35">
         <f>+D2778*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>816.98973855193481</v>
+        <v>820.97505434975005</v>
       </c>
       <c r="E2779" s="35">
         <f>+E2778*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48476,7 +48476,7 @@
       </c>
       <c r="D2780" s="35">
         <f>+D2779*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>817.4341203849566</v>
+        <v>821.42160389903052</v>
       </c>
       <c r="E2780" s="35">
         <f>+E2779*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48493,7 +48493,7 @@
       </c>
       <c r="D2781" s="35">
         <f>+D2780*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>817.87874392874198</v>
+        <v>821.86839633815134</v>
       </c>
       <c r="E2781" s="35">
         <f>+E2780*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48510,7 +48510,7 @@
       </c>
       <c r="D2782" s="35">
         <f>+D2781*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>818.32360931476364</v>
+        <v>822.31543179922676</v>
       </c>
       <c r="E2782" s="35">
         <f>+E2781*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48527,7 +48527,7 @@
       </c>
       <c r="D2783" s="35">
         <f>+D2782*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>818.76871667456578</v>
+        <v>822.76271041444261</v>
       </c>
       <c r="E2783" s="35">
         <f>+E2782*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48544,7 +48544,7 @@
       </c>
       <c r="D2784" s="35">
         <f>+D2783*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>819.21406613976421</v>
+        <v>823.2102323160567</v>
       </c>
       <c r="E2784" s="35">
         <f>+E2783*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="D2785" s="35">
         <f>+D2784*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>819.65965784204639</v>
+        <v>823.65799763639882</v>
       </c>
       <c r="E2785" s="35">
         <f>+E2784*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48578,7 +48578,7 @@
       </c>
       <c r="D2786" s="35">
         <f>+D2785*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>820.10549191317125</v>
+        <v>824.10600650787069</v>
       </c>
       <c r="E2786" s="35">
         <f>+E2785*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48595,7 +48595,7 @@
       </c>
       <c r="D2787" s="35">
         <f>+D2786*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>820.55156848496949</v>
+        <v>824.55425906294602</v>
       </c>
       <c r="E2787" s="35">
         <f>+E2786*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48612,7 +48612,7 @@
       </c>
       <c r="D2788" s="35">
         <f>+D2787*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>820.99788768934354</v>
+        <v>825.00275543417069</v>
       </c>
       <c r="E2788" s="35">
         <f>+E2787*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="D2789" s="35">
         <f>+D2788*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>821.44444965826744</v>
+        <v>825.45149575416258</v>
       </c>
       <c r="E2789" s="35">
         <f>+E2788*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48646,7 +48646,7 @@
       </c>
       <c r="D2790" s="35">
         <f>+D2789*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>821.89125452378721</v>
+        <v>825.90048015561172</v>
       </c>
       <c r="E2790" s="35">
         <f>+E2789*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48663,7 +48663,7 @@
       </c>
       <c r="D2791" s="35">
         <f>+D2790*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>822.33830241802048</v>
+        <v>826.34970877128023</v>
       </c>
       <c r="E2791" s="35">
         <f>+E2790*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48680,7 +48680,7 @@
       </c>
       <c r="D2792" s="35">
         <f>+D2791*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>822.78559347315695</v>
+        <v>826.79918173400267</v>
       </c>
       <c r="E2792" s="35">
         <f>+E2791*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48697,7 +48697,7 @@
       </c>
       <c r="D2793" s="35">
         <f>+D2792*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>823.23312782145808</v>
+        <v>827.24889917668565</v>
       </c>
       <c r="E2793" s="35">
         <f>+E2792*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48714,7 +48714,7 @@
       </c>
       <c r="D2794" s="35">
         <f>+D2793*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>823.68090559525729</v>
+        <v>827.69886123230822</v>
       </c>
       <c r="E2794" s="35">
         <f>+E2793*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48731,7 +48731,7 @@
       </c>
       <c r="D2795" s="35">
         <f>+D2794*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>824.12892692695993</v>
+        <v>828.14906803392159</v>
       </c>
       <c r="E2795" s="35">
         <f>+E2794*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48748,7 +48748,7 @@
       </c>
       <c r="D2796" s="35">
         <f>+D2795*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>824.57719194904359</v>
+        <v>828.59951971464955</v>
       </c>
       <c r="E2796" s="35">
         <f>+E2795*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48765,7 +48765,7 @@
       </c>
       <c r="D2797" s="35">
         <f>+D2796*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>825.02570079405768</v>
+        <v>829.05021640768803</v>
       </c>
       <c r="E2797" s="35">
         <f>+E2796*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48782,7 +48782,7 @@
       </c>
       <c r="D2798" s="35">
         <f>+D2797*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>825.47445359462381</v>
+        <v>829.50115824630564</v>
       </c>
       <c r="E2798" s="35">
         <f>+E2797*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48799,7 +48799,7 @@
       </c>
       <c r="D2799" s="35">
         <f>+D2798*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>825.92345048343566</v>
+        <v>829.95234536384339</v>
       </c>
       <c r="E2799" s="35">
         <f>+E2798*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48816,7 +48816,7 @@
       </c>
       <c r="D2800" s="35">
         <f>+D2799*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>826.37269159325922</v>
+        <v>830.40377789371485</v>
       </c>
       <c r="E2800" s="35">
         <f>+E2799*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48833,7 +48833,7 @@
       </c>
       <c r="D2801" s="35">
         <f>+D2800*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>826.82217705693256</v>
+        <v>830.85545596940608</v>
       </c>
       <c r="E2801" s="35">
         <f>+E2800*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="D2802" s="35">
         <f>+D2801*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>827.27190700736605</v>
+        <v>831.30737972447582</v>
       </c>
       <c r="E2802" s="35">
         <f>+E2801*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48867,7 +48867,7 @@
       </c>
       <c r="D2803" s="35">
         <f>+D2802*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>827.72188157754238</v>
+        <v>831.75954929255545</v>
       </c>
       <c r="E2803" s="35">
         <f>+E2802*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48884,7 +48884,7 @@
       </c>
       <c r="D2804" s="35">
         <f>+D2803*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>828.17210090051651</v>
+        <v>832.21196480734898</v>
       </c>
       <c r="E2804" s="35">
         <f>+E2803*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48901,7 +48901,7 @@
       </c>
       <c r="D2805" s="35">
         <f>+D2804*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>828.62256510941586</v>
+        <v>832.66462640263319</v>
       </c>
       <c r="E2805" s="35">
         <f>+E2804*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48918,7 +48918,7 @@
       </c>
       <c r="D2806" s="35">
         <f>+D2805*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>829.07327433744013</v>
+        <v>833.11753421225762</v>
       </c>
       <c r="E2806" s="35">
         <f>+E2805*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48935,7 +48935,7 @@
       </c>
       <c r="D2807" s="35">
         <f>+D2806*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>829.52422871786166</v>
+        <v>833.57068837014458</v>
       </c>
       <c r="E2807" s="35">
         <f>+E2806*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48952,7 +48952,7 @@
       </c>
       <c r="D2808" s="35">
         <f>+D2807*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>829.97542838402512</v>
+        <v>834.02408901028934</v>
       </c>
       <c r="E2808" s="35">
         <f>+E2807*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48969,7 +48969,7 @@
       </c>
       <c r="D2809" s="35">
         <f>+D2808*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>830.42687346934781</v>
+        <v>834.47773626675996</v>
       </c>
       <c r="E2809" s="35">
         <f>+E2808*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48986,7 +48986,7 @@
       </c>
       <c r="D2810" s="35">
         <f>+D2809*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>830.87856410731945</v>
+        <v>834.93163027369735</v>
       </c>
       <c r="E2810" s="35">
         <f>+E2809*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49003,7 +49003,7 @@
       </c>
       <c r="D2811" s="35">
         <f>+D2810*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>831.33050043150263</v>
+        <v>835.38577116531553</v>
       </c>
       <c r="E2811" s="35">
         <f>+E2810*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49020,7 +49020,7 @@
       </c>
       <c r="D2812" s="35">
         <f>+D2811*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>831.78268257553236</v>
+        <v>835.8401590759014</v>
       </c>
       <c r="E2812" s="35">
         <f>+E2811*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49037,7 +49037,7 @@
       </c>
       <c r="D2813" s="35">
         <f>+D2812*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>832.23511067311631</v>
+        <v>836.29479413981505</v>
       </c>
       <c r="E2813" s="35">
         <f>+E2812*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49054,7 +49054,7 @@
       </c>
       <c r="D2814" s="35">
         <f>+D2813*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>832.68778485803512</v>
+        <v>836.74967649148948</v>
       </c>
       <c r="E2814" s="35">
         <f>+E2813*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49071,7 +49071,7 @@
       </c>
       <c r="D2815" s="35">
         <f>+D2814*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>833.14070526414196</v>
+        <v>837.20480626543099</v>
       </c>
       <c r="E2815" s="35">
         <f>+E2814*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49088,7 +49088,7 @@
       </c>
       <c r="D2816" s="35">
         <f>+D2815*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>833.59387202536288</v>
+        <v>837.66018359621887</v>
       </c>
       <c r="E2816" s="35">
         <f>+E2815*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49105,7 +49105,7 @@
       </c>
       <c r="D2817" s="35">
         <f>+D2816*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>834.04728527569682</v>
+        <v>838.11580861850575</v>
       </c>
       <c r="E2817" s="35">
         <f>+E2816*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49122,7 +49122,7 @@
       </c>
       <c r="D2818" s="35">
         <f>+D2817*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>834.50094514921568</v>
+        <v>838.57168146701736</v>
       </c>
       <c r="E2818" s="35">
         <f>+E2817*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49139,7 +49139,7 @@
       </c>
       <c r="D2819" s="35">
         <f>+D2818*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>834.95485178006402</v>
+        <v>839.02780227655285</v>
       </c>
       <c r="E2819" s="35">
         <f>+E2818*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49156,7 +49156,7 @@
       </c>
       <c r="D2820" s="35">
         <f>+D2819*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>835.4090053024596</v>
+        <v>839.48417118198461</v>
       </c>
       <c r="E2820" s="35">
         <f>+E2819*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49173,7 +49173,7 @@
       </c>
       <c r="D2821" s="35">
         <f>+D2820*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>835.8634058506932</v>
+        <v>839.94078831825834</v>
       </c>
       <c r="E2821" s="35">
         <f>+E2820*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49190,7 +49190,7 @@
       </c>
       <c r="D2822" s="35">
         <f>+D2821*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>836.31805355912843</v>
+        <v>840.39765382039332</v>
       </c>
       <c r="E2822" s="35">
         <f>+E2821*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49207,7 +49207,7 @@
       </c>
       <c r="D2823" s="35">
         <f>+D2822*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>836.77294856220215</v>
+        <v>840.85476782348212</v>
       </c>
       <c r="E2823" s="35">
         <f>+E2822*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49224,7 +49224,7 @@
       </c>
       <c r="D2824" s="35">
         <f>+D2823*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>837.22809099442429</v>
+        <v>841.31213046269079</v>
       </c>
       <c r="E2824" s="35">
         <f>+E2823*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49241,7 +49241,7 @@
       </c>
       <c r="D2825" s="35">
         <f>+D2824*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>837.68348099037803</v>
+        <v>841.76974187325891</v>
       </c>
       <c r="E2825" s="35">
         <f>+E2824*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49258,7 +49258,7 @@
       </c>
       <c r="D2826" s="35">
         <f>+D2825*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>838.13911868471962</v>
+        <v>842.22760219049974</v>
       </c>
       <c r="E2826" s="35">
         <f>+E2825*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49275,7 +49275,7 @@
       </c>
       <c r="D2827" s="35">
         <f>+D2826*((1+INFLA!$C$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
-        <v>838.59500421217865</v>
+        <v>842.68571154980009</v>
       </c>
       <c r="E2827" s="35">
         <f>+E2826*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49289,14 +49289,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33790591-3D3C-4B54-B1B9-5A6FCD41E661}">
-  <dimension ref="A2:D16"/>
+  <dimension ref="A2:H16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -49310,7 +49310,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="25">
         <v>46023</v>
       </c>
@@ -49322,7 +49322,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>46054</v>
       </c>
@@ -49334,7 +49334,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <v>46082</v>
       </c>
@@ -49342,13 +49342,13 @@
         <v>2.7E-2</v>
       </c>
       <c r="C5" s="45">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="D5" s="44">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>46113</v>
       </c>
@@ -49362,7 +49362,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <v>46143</v>
       </c>
@@ -49376,7 +49376,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>46174</v>
       </c>
@@ -49390,7 +49390,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>46204</v>
       </c>
@@ -49404,7 +49404,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>46235</v>
       </c>
@@ -49418,7 +49418,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>46266</v>
       </c>
@@ -49430,7 +49430,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>46296</v>
       </c>
@@ -49441,8 +49441,12 @@
       <c r="D12" s="44">
         <v>1.9E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f>20025872*0.995</f>
+        <v>19925742.640000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <v>46327</v>
       </c>
@@ -49453,8 +49457,11 @@
       <c r="D13" s="44">
         <v>1.9E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <v>46357</v>
       </c>
@@ -49465,12 +49472,16 @@
       <c r="D14" s="44">
         <v>1.7999999999999999E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f>+H12/H13</f>
+        <v>22798.332540045769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="27"/>
       <c r="D15" s="34"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D16" s="28">
         <v>0.32</v>
       </c>
@@ -49486,12 +49497,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -49584,12 +49595,12 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
       <c r="H8" s="10">
         <v>45596</v>
       </c>
@@ -49662,12 +49673,12 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
       <c r="H13" s="8">
         <v>45323</v>
       </c>
@@ -49740,12 +49751,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
       <c r="H18" s="10">
         <v>37986</v>
       </c>
@@ -49818,12 +49829,12 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -49864,12 +49875,12 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -49910,12 +49921,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -49956,12 +49967,12 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
@@ -50002,12 +50013,12 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="46" t="s">
+      <c r="A43" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -50048,12 +50059,12 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
@@ -50094,12 +50105,12 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="46" t="s">
+      <c r="A53" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="47"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
@@ -50140,12 +50151,12 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="47"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
@@ -50187,12 +50198,12 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="46" t="s">
+      <c r="A63" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="47"/>
-      <c r="C63" s="47"/>
-      <c r="D63" s="47"/>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
@@ -50268,12 +50279,12 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="46" t="s">
+      <c r="A70" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
@@ -50417,12 +50428,12 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="46" t="s">
+      <c r="A81" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="47"/>
-      <c r="C81" s="47"/>
-      <c r="D81" s="47"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="48"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
@@ -50659,12 +50670,12 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="46" t="s">
+      <c r="A98" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B98" s="47"/>
-      <c r="C98" s="47"/>
-      <c r="D98" s="47"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
+      <c r="D98" s="48"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
@@ -50978,12 +50989,12 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="46" t="s">
+      <c r="A119" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="B119" s="47"/>
-      <c r="C119" s="47"/>
-      <c r="D119" s="47"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="48"/>
+      <c r="D119" s="48"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
@@ -51463,12 +51474,12 @@
       <c r="A150" s="6"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="46" t="s">
+      <c r="A151" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B151" s="47"/>
-      <c r="C151" s="47"/>
-      <c r="D151" s="47"/>
+      <c r="B151" s="48"/>
+      <c r="C151" s="48"/>
+      <c r="D151" s="48"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
@@ -52127,12 +52138,12 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="46" t="s">
+      <c r="A196" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B196" s="47"/>
-      <c r="C196" s="47"/>
-      <c r="D196" s="47"/>
+      <c r="B196" s="48"/>
+      <c r="C196" s="48"/>
+      <c r="D196" s="48"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
@@ -52299,12 +52310,12 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="46" t="s">
+      <c r="A209" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B209" s="47"/>
-      <c r="C209" s="47"/>
-      <c r="D209" s="47"/>
+      <c r="B209" s="48"/>
+      <c r="C209" s="48"/>
+      <c r="D209" s="48"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
@@ -52382,6 +52393,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52397,11 +52413,6 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/ssegura_balanz_com/Documents/Escritorio/curvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D59E1ED-A355-46FA-B65C-3C1C5E2ADD39}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D50BF706-7330-419B-A635-7AD685809D9F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
@@ -168,7 +168,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +238,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF003A70"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <sz val="9"/>
@@ -383,7 +388,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -501,6 +506,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -45803,12 +45820,11 @@
       </c>
     </row>
     <row r="2645" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2645" s="22">
+      <c r="A2645" s="49">
         <v>46128</v>
       </c>
-      <c r="B2645" s="35" t="e">
-        <f>+B2644*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2645" s="50">
+        <v>746.38092265237003</v>
       </c>
       <c r="C2645" s="35">
         <f>+C2644*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45824,12 +45840,11 @@
       </c>
     </row>
     <row r="2646" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2646" s="22">
+      <c r="A2646" s="51">
         <v>46129</v>
       </c>
-      <c r="B2646" s="35" t="e">
-        <f>+B2645*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2646" s="52">
+        <v>747.21322232958005</v>
       </c>
       <c r="C2646" s="35">
         <f>+C2645*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45845,12 +45860,11 @@
       </c>
     </row>
     <row r="2647" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2647" s="22">
+      <c r="A2647" s="49">
         <v>46130</v>
       </c>
-      <c r="B2647" s="35" t="e">
-        <f>+B2646*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2647" s="50">
+        <v>748.04645011565003</v>
       </c>
       <c r="C2647" s="35">
         <f>+C2646*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45867,12 +45881,11 @@
       <c r="F2647" s="31"/>
     </row>
     <row r="2648" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2648" s="22">
+      <c r="A2648" s="51">
         <v>46131</v>
       </c>
-      <c r="B2648" s="35" t="e">
-        <f>+B2647*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2648" s="52">
+        <v>748.88060704553004</v>
       </c>
       <c r="C2648" s="35">
         <f>+C2647*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45889,12 +45902,11 @@
       <c r="F2648" s="31"/>
     </row>
     <row r="2649" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2649" s="22">
+      <c r="A2649" s="49">
         <v>46132</v>
       </c>
-      <c r="B2649" s="35" t="e">
-        <f>+B2648*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2649" s="50">
+        <v>749.71569415532997</v>
       </c>
       <c r="C2649" s="35">
         <f>+C2648*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45910,12 +45922,11 @@
       </c>
     </row>
     <row r="2650" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2650" s="22">
+      <c r="A2650" s="51">
         <v>46133</v>
       </c>
-      <c r="B2650" s="35" t="e">
-        <f>+B2649*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2650" s="52">
+        <v>750.55171248229999</v>
       </c>
       <c r="C2650" s="35">
         <f>+C2649*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45932,12 +45943,11 @@
       <c r="F2650" s="33"/>
     </row>
     <row r="2651" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2651" s="22">
+      <c r="A2651" s="49">
         <v>46134</v>
       </c>
-      <c r="B2651" s="35" t="e">
-        <f>+B2650*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2651" s="50">
+        <v>751.38866306486</v>
       </c>
       <c r="C2651" s="35">
         <f>+C2650*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45953,12 +45963,11 @@
       </c>
     </row>
     <row r="2652" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2652" s="22">
+      <c r="A2652" s="51">
         <v>46135</v>
       </c>
-      <c r="B2652" s="35" t="e">
-        <f>+B2651*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2652" s="52">
+        <v>752.22654694257994</v>
       </c>
       <c r="C2652" s="35">
         <f>+C2651*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45975,12 +45984,11 @@
       <c r="F2652" s="34"/>
     </row>
     <row r="2653" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2653" s="22">
+      <c r="A2653" s="49">
         <v>46136</v>
       </c>
-      <c r="B2653" s="35" t="e">
-        <f>+B2652*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2653" s="50">
+        <v>753.06536515617995</v>
       </c>
       <c r="C2653" s="35">
         <f>+C2652*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -45996,12 +46004,11 @@
       </c>
     </row>
     <row r="2654" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2654" s="22">
+      <c r="A2654" s="51">
         <v>46137</v>
       </c>
-      <c r="B2654" s="35" t="e">
-        <f>+B2653*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2654" s="52">
+        <v>753.90511874754998</v>
       </c>
       <c r="C2654" s="35">
         <f>+C2653*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46017,12 +46024,11 @@
       </c>
     </row>
     <row r="2655" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2655" s="22">
+      <c r="A2655" s="49">
         <v>46138</v>
       </c>
-      <c r="B2655" s="35" t="e">
-        <f>+B2654*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2655" s="50">
+        <v>754.74580875976005</v>
       </c>
       <c r="C2655" s="35">
         <f>+C2654*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46038,12 +46044,11 @@
       </c>
     </row>
     <row r="2656" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2656" s="22">
+      <c r="A2656" s="51">
         <v>46139</v>
       </c>
-      <c r="B2656" s="35" t="e">
-        <f>+B2655*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2656" s="52">
+        <v>755.58743623701002</v>
       </c>
       <c r="C2656" s="35">
         <f>+C2655*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46059,12 +46064,11 @@
       </c>
     </row>
     <row r="2657" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2657" s="22">
+      <c r="A2657" s="49">
         <v>46140</v>
       </c>
-      <c r="B2657" s="35" t="e">
-        <f>+B2656*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2657" s="50">
+        <v>756.43000222469004</v>
       </c>
       <c r="C2657" s="35">
         <f>+C2656*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46080,12 +46084,11 @@
       </c>
     </row>
     <row r="2658" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2658" s="22">
+      <c r="A2658" s="51">
         <v>46141</v>
       </c>
-      <c r="B2658" s="35" t="e">
-        <f>+B2657*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2658" s="52">
+        <v>757.27350776933997</v>
       </c>
       <c r="C2658" s="35">
         <f>+C2657*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46101,12 +46104,11 @@
       </c>
     </row>
     <row r="2659" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2659" s="22">
+      <c r="A2659" s="49">
         <v>46142</v>
       </c>
-      <c r="B2659" s="35" t="e">
-        <f>+B2658*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2659" s="50">
+        <v>758.11795391867997</v>
       </c>
       <c r="C2659" s="35">
         <f>+C2658*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46122,12 +46124,11 @@
       </c>
     </row>
     <row r="2660" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2660" s="22">
+      <c r="A2660" s="51">
         <v>46143</v>
       </c>
-      <c r="B2660" s="35" t="e">
-        <f>+B2659*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2660" s="52">
+        <v>758.96334172158004</v>
       </c>
       <c r="C2660" s="35">
         <f>+C2659*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46143,12 +46144,11 @@
       </c>
     </row>
     <row r="2661" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2661" s="22">
+      <c r="A2661" s="49">
         <v>46144</v>
       </c>
-      <c r="B2661" s="35" t="e">
-        <f>+B2660*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2661" s="50">
+        <v>759.8096722281</v>
       </c>
       <c r="C2661" s="35">
         <f>+C2660*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46164,12 +46164,11 @@
       </c>
     </row>
     <row r="2662" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2662" s="22">
+      <c r="A2662" s="51">
         <v>46145</v>
       </c>
-      <c r="B2662" s="35" t="e">
-        <f>+B2661*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2662" s="52">
+        <v>760.65694648944998</v>
       </c>
       <c r="C2662" s="35">
         <f>+C2661*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46185,12 +46184,11 @@
       </c>
     </row>
     <row r="2663" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2663" s="22">
+      <c r="A2663" s="49">
         <v>46146</v>
       </c>
-      <c r="B2663" s="35" t="e">
-        <f>+B2662*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2663" s="50">
+        <v>761.50516555803995</v>
       </c>
       <c r="C2663" s="35">
         <f>+C2662*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46207,12 +46205,11 @@
       <c r="F2663" s="16"/>
     </row>
     <row r="2664" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2664" s="22">
+      <c r="A2664" s="51">
         <v>46147</v>
       </c>
-      <c r="B2664" s="35" t="e">
-        <f>+B2663*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2664" s="52">
+        <v>762.35433048744005</v>
       </c>
       <c r="C2664" s="35">
         <f>+C2663*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46228,12 +46225,11 @@
       </c>
     </row>
     <row r="2665" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2665" s="22">
+      <c r="A2665" s="49">
         <v>46148</v>
       </c>
-      <c r="B2665" s="35" t="e">
-        <f>+B2664*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2665" s="50">
+        <v>763.20444233237004</v>
       </c>
       <c r="C2665" s="35">
         <f>+C2664*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46249,12 +46245,11 @@
       </c>
     </row>
     <row r="2666" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2666" s="22">
+      <c r="A2666" s="51">
         <v>46149</v>
       </c>
-      <c r="B2666" s="35" t="e">
-        <f>+B2665*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2666" s="52">
+        <v>764.05550214875996</v>
       </c>
       <c r="C2666" s="35">
         <f>+C2665*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46270,12 +46265,11 @@
       </c>
     </row>
     <row r="2667" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2667" s="22">
+      <c r="A2667" s="49">
         <v>46150</v>
       </c>
-      <c r="B2667" s="35" t="e">
-        <f>+B2666*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2667" s="50">
+        <v>764.90751099372005</v>
       </c>
       <c r="C2667" s="35">
         <f>+C2666*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46291,12 +46285,11 @@
       </c>
     </row>
     <row r="2668" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2668" s="22">
+      <c r="A2668" s="51">
         <v>46151</v>
       </c>
-      <c r="B2668" s="35" t="e">
-        <f>+B2667*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2668" s="52">
+        <v>765.76046992550005</v>
       </c>
       <c r="C2668" s="35">
         <f>+C2667*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46312,12 +46305,11 @@
       </c>
     </row>
     <row r="2669" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2669" s="22">
+      <c r="A2669" s="49">
         <v>46152</v>
       </c>
-      <c r="B2669" s="35" t="e">
-        <f>+B2668*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2669" s="50">
+        <v>766.61438000357998</v>
       </c>
       <c r="C2669" s="35">
         <f>+C2668*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46333,12 +46325,11 @@
       </c>
     </row>
     <row r="2670" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2670" s="22">
+      <c r="A2670" s="51">
         <v>46153</v>
       </c>
-      <c r="B2670" s="35" t="e">
-        <f>+B2669*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2670" s="52">
+        <v>767.46924228856994</v>
       </c>
       <c r="C2670" s="35">
         <f>+C2669*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46354,12 +46345,11 @@
       </c>
     </row>
     <row r="2671" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2671" s="22">
+      <c r="A2671" s="49">
         <v>46154</v>
       </c>
-      <c r="B2671" s="35" t="e">
-        <f>+B2670*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2671" s="50">
+        <v>768.32505784231</v>
       </c>
       <c r="C2671" s="35">
         <f>+C2670*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46375,12 +46365,11 @@
       </c>
     </row>
     <row r="2672" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2672" s="22">
+      <c r="A2672" s="51">
         <v>46155</v>
       </c>
-      <c r="B2672" s="35" t="e">
-        <f>+B2671*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2672" s="52">
+        <v>769.18182772780006</v>
       </c>
       <c r="C2672" s="35">
         <f>+C2671*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46396,12 +46385,11 @@
       </c>
     </row>
     <row r="2673" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2673" s="22">
+      <c r="A2673" s="49">
         <v>46156</v>
       </c>
-      <c r="B2673" s="35" t="e">
-        <f>+B2672*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2673" s="50">
+        <v>770.03955300921996</v>
       </c>
       <c r="C2673" s="35">
         <f>+C2672*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -46417,12 +46405,11 @@
       </c>
     </row>
     <row r="2674" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2674" s="29">
+      <c r="A2674" s="51">
         <v>46157</v>
       </c>
-      <c r="B2674" s="35" t="e">
-        <f>+B2673*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2674" s="52">
+        <v>770.89823475194999</v>
       </c>
       <c r="C2674" s="35">
         <f>+C2673*((1+INFLA!$B$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
@@ -52393,11 +52380,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52413,6 +52395,11 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -502,10 +502,6 @@
     <xf numFmtId="14" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -518,6 +514,10 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -535,10 +535,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45820,10 +45816,10 @@
       </c>
     </row>
     <row r="2645" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2645" s="49">
+      <c r="A2645" s="47">
         <v>46128</v>
       </c>
-      <c r="B2645" s="50">
+      <c r="B2645" s="48">
         <v>746.38092265237003</v>
       </c>
       <c r="C2645" s="35">
@@ -45840,10 +45836,10 @@
       </c>
     </row>
     <row r="2646" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2646" s="51">
+      <c r="A2646" s="49">
         <v>46129</v>
       </c>
-      <c r="B2646" s="52">
+      <c r="B2646" s="50">
         <v>747.21322232958005</v>
       </c>
       <c r="C2646" s="35">
@@ -45860,10 +45856,10 @@
       </c>
     </row>
     <row r="2647" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2647" s="49">
+      <c r="A2647" s="47">
         <v>46130</v>
       </c>
-      <c r="B2647" s="50">
+      <c r="B2647" s="48">
         <v>748.04645011565003</v>
       </c>
       <c r="C2647" s="35">
@@ -45881,10 +45877,10 @@
       <c r="F2647" s="31"/>
     </row>
     <row r="2648" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2648" s="51">
+      <c r="A2648" s="49">
         <v>46131</v>
       </c>
-      <c r="B2648" s="52">
+      <c r="B2648" s="50">
         <v>748.88060704553004</v>
       </c>
       <c r="C2648" s="35">
@@ -45902,10 +45898,10 @@
       <c r="F2648" s="31"/>
     </row>
     <row r="2649" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2649" s="49">
+      <c r="A2649" s="47">
         <v>46132</v>
       </c>
-      <c r="B2649" s="50">
+      <c r="B2649" s="48">
         <v>749.71569415532997</v>
       </c>
       <c r="C2649" s="35">
@@ -45922,10 +45918,10 @@
       </c>
     </row>
     <row r="2650" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2650" s="51">
+      <c r="A2650" s="49">
         <v>46133</v>
       </c>
-      <c r="B2650" s="52">
+      <c r="B2650" s="50">
         <v>750.55171248229999</v>
       </c>
       <c r="C2650" s="35">
@@ -45943,10 +45939,10 @@
       <c r="F2650" s="33"/>
     </row>
     <row r="2651" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2651" s="49">
+      <c r="A2651" s="47">
         <v>46134</v>
       </c>
-      <c r="B2651" s="50">
+      <c r="B2651" s="48">
         <v>751.38866306486</v>
       </c>
       <c r="C2651" s="35">
@@ -45963,10 +45959,10 @@
       </c>
     </row>
     <row r="2652" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2652" s="51">
+      <c r="A2652" s="49">
         <v>46135</v>
       </c>
-      <c r="B2652" s="52">
+      <c r="B2652" s="50">
         <v>752.22654694257994</v>
       </c>
       <c r="C2652" s="35">
@@ -45984,10 +45980,10 @@
       <c r="F2652" s="34"/>
     </row>
     <row r="2653" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2653" s="49">
+      <c r="A2653" s="47">
         <v>46136</v>
       </c>
-      <c r="B2653" s="50">
+      <c r="B2653" s="48">
         <v>753.06536515617995</v>
       </c>
       <c r="C2653" s="35">
@@ -46004,10 +46000,10 @@
       </c>
     </row>
     <row r="2654" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2654" s="51">
+      <c r="A2654" s="49">
         <v>46137</v>
       </c>
-      <c r="B2654" s="52">
+      <c r="B2654" s="50">
         <v>753.90511874754998</v>
       </c>
       <c r="C2654" s="35">
@@ -46024,10 +46020,10 @@
       </c>
     </row>
     <row r="2655" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2655" s="49">
+      <c r="A2655" s="47">
         <v>46138</v>
       </c>
-      <c r="B2655" s="50">
+      <c r="B2655" s="48">
         <v>754.74580875976005</v>
       </c>
       <c r="C2655" s="35">
@@ -46044,10 +46040,10 @@
       </c>
     </row>
     <row r="2656" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2656" s="51">
+      <c r="A2656" s="49">
         <v>46139</v>
       </c>
-      <c r="B2656" s="52">
+      <c r="B2656" s="50">
         <v>755.58743623701002</v>
       </c>
       <c r="C2656" s="35">
@@ -46064,10 +46060,10 @@
       </c>
     </row>
     <row r="2657" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2657" s="49">
+      <c r="A2657" s="47">
         <v>46140</v>
       </c>
-      <c r="B2657" s="50">
+      <c r="B2657" s="48">
         <v>756.43000222469004</v>
       </c>
       <c r="C2657" s="35">
@@ -46084,10 +46080,10 @@
       </c>
     </row>
     <row r="2658" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2658" s="51">
+      <c r="A2658" s="49">
         <v>46141</v>
       </c>
-      <c r="B2658" s="52">
+      <c r="B2658" s="50">
         <v>757.27350776933997</v>
       </c>
       <c r="C2658" s="35">
@@ -46104,10 +46100,10 @@
       </c>
     </row>
     <row r="2659" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2659" s="49">
+      <c r="A2659" s="47">
         <v>46142</v>
       </c>
-      <c r="B2659" s="50">
+      <c r="B2659" s="48">
         <v>758.11795391867997</v>
       </c>
       <c r="C2659" s="35">
@@ -46124,10 +46120,10 @@
       </c>
     </row>
     <row r="2660" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2660" s="51">
+      <c r="A2660" s="49">
         <v>46143</v>
       </c>
-      <c r="B2660" s="52">
+      <c r="B2660" s="50">
         <v>758.96334172158004</v>
       </c>
       <c r="C2660" s="35">
@@ -46144,10 +46140,10 @@
       </c>
     </row>
     <row r="2661" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2661" s="49">
+      <c r="A2661" s="47">
         <v>46144</v>
       </c>
-      <c r="B2661" s="50">
+      <c r="B2661" s="48">
         <v>759.8096722281</v>
       </c>
       <c r="C2661" s="35">
@@ -46164,10 +46160,10 @@
       </c>
     </row>
     <row r="2662" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2662" s="51">
+      <c r="A2662" s="49">
         <v>46145</v>
       </c>
-      <c r="B2662" s="52">
+      <c r="B2662" s="50">
         <v>760.65694648944998</v>
       </c>
       <c r="C2662" s="35">
@@ -46184,10 +46180,10 @@
       </c>
     </row>
     <row r="2663" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2663" s="49">
+      <c r="A2663" s="47">
         <v>46146</v>
       </c>
-      <c r="B2663" s="50">
+      <c r="B2663" s="48">
         <v>761.50516555803995</v>
       </c>
       <c r="C2663" s="35">
@@ -46205,10 +46201,10 @@
       <c r="F2663" s="16"/>
     </row>
     <row r="2664" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2664" s="51">
+      <c r="A2664" s="49">
         <v>46147</v>
       </c>
-      <c r="B2664" s="52">
+      <c r="B2664" s="50">
         <v>762.35433048744005</v>
       </c>
       <c r="C2664" s="35">
@@ -46225,10 +46221,10 @@
       </c>
     </row>
     <row r="2665" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2665" s="49">
+      <c r="A2665" s="47">
         <v>46148</v>
       </c>
-      <c r="B2665" s="50">
+      <c r="B2665" s="48">
         <v>763.20444233237004</v>
       </c>
       <c r="C2665" s="35">
@@ -46245,10 +46241,10 @@
       </c>
     </row>
     <row r="2666" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2666" s="51">
+      <c r="A2666" s="49">
         <v>46149</v>
       </c>
-      <c r="B2666" s="52">
+      <c r="B2666" s="50">
         <v>764.05550214875996</v>
       </c>
       <c r="C2666" s="35">
@@ -46265,10 +46261,10 @@
       </c>
     </row>
     <row r="2667" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2667" s="49">
+      <c r="A2667" s="47">
         <v>46150</v>
       </c>
-      <c r="B2667" s="50">
+      <c r="B2667" s="48">
         <v>764.90751099372005</v>
       </c>
       <c r="C2667" s="35">
@@ -46285,10 +46281,10 @@
       </c>
     </row>
     <row r="2668" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2668" s="51">
+      <c r="A2668" s="49">
         <v>46151</v>
       </c>
-      <c r="B2668" s="52">
+      <c r="B2668" s="50">
         <v>765.76046992550005</v>
       </c>
       <c r="C2668" s="35">
@@ -46305,10 +46301,10 @@
       </c>
     </row>
     <row r="2669" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2669" s="49">
+      <c r="A2669" s="47">
         <v>46152</v>
       </c>
-      <c r="B2669" s="50">
+      <c r="B2669" s="48">
         <v>766.61438000357998</v>
       </c>
       <c r="C2669" s="35">
@@ -46325,10 +46321,10 @@
       </c>
     </row>
     <row r="2670" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2670" s="51">
+      <c r="A2670" s="49">
         <v>46153</v>
       </c>
-      <c r="B2670" s="52">
+      <c r="B2670" s="50">
         <v>767.46924228856994</v>
       </c>
       <c r="C2670" s="35">
@@ -46345,10 +46341,10 @@
       </c>
     </row>
     <row r="2671" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2671" s="49">
+      <c r="A2671" s="47">
         <v>46154</v>
       </c>
-      <c r="B2671" s="50">
+      <c r="B2671" s="48">
         <v>768.32505784231</v>
       </c>
       <c r="C2671" s="35">
@@ -46365,10 +46361,10 @@
       </c>
     </row>
     <row r="2672" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2672" s="51">
+      <c r="A2672" s="49">
         <v>46155</v>
       </c>
-      <c r="B2672" s="52">
+      <c r="B2672" s="50">
         <v>769.18182772780006</v>
       </c>
       <c r="C2672" s="35">
@@ -46385,10 +46381,10 @@
       </c>
     </row>
     <row r="2673" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2673" s="49">
+      <c r="A2673" s="47">
         <v>46156</v>
       </c>
-      <c r="B2673" s="50">
+      <c r="B2673" s="48">
         <v>770.03955300921996</v>
       </c>
       <c r="C2673" s="35">
@@ -46405,10 +46401,10 @@
       </c>
     </row>
     <row r="2674" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2674" s="51">
+      <c r="A2674" s="49">
         <v>46157</v>
       </c>
-      <c r="B2674" s="52">
+      <c r="B2674" s="50">
         <v>770.89823475194999</v>
       </c>
       <c r="C2674" s="35">
@@ -49484,12 +49480,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -49582,12 +49578,12 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
       <c r="H8" s="10">
         <v>45596</v>
       </c>
@@ -49660,12 +49656,12 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
       <c r="H13" s="8">
         <v>45323</v>
       </c>
@@ -49738,12 +49734,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
       <c r="H18" s="10">
         <v>37986</v>
       </c>
@@ -49816,12 +49812,12 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -49862,12 +49858,12 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -49908,12 +49904,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -49954,12 +49950,12 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="47" t="s">
+      <c r="A38" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
@@ -50000,12 +49996,12 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="47" t="s">
+      <c r="A43" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -50046,12 +50042,12 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="47" t="s">
+      <c r="A48" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
@@ -50092,12 +50088,12 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="47" t="s">
+      <c r="A53" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="48"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
@@ -50138,12 +50134,12 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="47" t="s">
+      <c r="A58" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="48"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
@@ -50185,12 +50181,12 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="47" t="s">
+      <c r="A63" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
@@ -50266,12 +50262,12 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="47" t="s">
+      <c r="A70" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
@@ -50415,12 +50411,12 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="47" t="s">
+      <c r="A81" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
@@ -50657,12 +50653,12 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="47" t="s">
+      <c r="A98" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B98" s="48"/>
-      <c r="C98" s="48"/>
-      <c r="D98" s="48"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
+      <c r="D98" s="52"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
@@ -50976,12 +50972,12 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="47" t="s">
+      <c r="A119" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B119" s="48"/>
-      <c r="C119" s="48"/>
-      <c r="D119" s="48"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="52"/>
+      <c r="D119" s="52"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
@@ -51461,12 +51457,12 @@
       <c r="A150" s="6"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="47" t="s">
+      <c r="A151" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B151" s="48"/>
-      <c r="C151" s="48"/>
-      <c r="D151" s="48"/>
+      <c r="B151" s="52"/>
+      <c r="C151" s="52"/>
+      <c r="D151" s="52"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
@@ -52125,12 +52121,12 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="47" t="s">
+      <c r="A196" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B196" s="48"/>
-      <c r="C196" s="48"/>
-      <c r="D196" s="48"/>
+      <c r="B196" s="52"/>
+      <c r="C196" s="52"/>
+      <c r="D196" s="52"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
@@ -52297,12 +52293,12 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="47" t="s">
+      <c r="A209" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B209" s="48"/>
-      <c r="C209" s="48"/>
-      <c r="D209" s="48"/>
+      <c r="B209" s="52"/>
+      <c r="C209" s="52"/>
+      <c r="D209" s="52"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
@@ -52380,6 +52376,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52395,11 +52396,6 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="434" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D50BF706-7330-419B-A635-7AD685809D9F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
+    <workbookView xWindow="1116" yWindow="0" windowWidth="17280" windowHeight="12336" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
   <sheets>
     <sheet name="CER" sheetId="2" r:id="rId1"/>
@@ -537,6 +537,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -52376,11 +52380,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52396,6 +52395,11 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/ssegura_balanz_com/Documents/Escritorio/curvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="434" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D50BF706-7330-419B-A635-7AD685809D9F}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80FA7194-CE52-402C-BC78-67D5A55CAA3D}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="0" windowWidth="17280" windowHeight="12336" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
   <sheets>
     <sheet name="CER" sheetId="2" r:id="rId1"/>
@@ -168,7 +168,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +238,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF003A70"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <sz val="9"/>
@@ -388,7 +393,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -518,6 +523,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -46425,12 +46442,11 @@
       </c>
     </row>
     <row r="2675" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2675" s="22">
+      <c r="A2675" s="53">
         <v>46158</v>
       </c>
-      <c r="B2675" s="35" t="e">
-        <f>+B2674*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2675" s="54">
+        <v>771.53679651802997</v>
       </c>
       <c r="C2675" s="35">
         <f>+C2674*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46446,12 +46462,11 @@
       </c>
     </row>
     <row r="2676" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2676" s="22">
+      <c r="A2676" s="55">
         <v>46159</v>
       </c>
-      <c r="B2676" s="35" t="e">
-        <f>+B2675*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2676" s="56">
+        <v>772.17588722697997</v>
       </c>
       <c r="C2676" s="35">
         <f>+C2675*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46467,12 +46482,11 @@
       </c>
     </row>
     <row r="2677" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2677" s="22">
+      <c r="A2677" s="53">
         <v>46160</v>
       </c>
-      <c r="B2677" s="35" t="e">
-        <f>+B2676*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2677" s="54">
+        <v>772.81550731695995</v>
       </c>
       <c r="C2677" s="35">
         <f>+C2676*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46488,12 +46502,11 @@
       </c>
     </row>
     <row r="2678" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2678" s="22">
+      <c r="A2678" s="55">
         <v>46161</v>
       </c>
-      <c r="B2678" s="35" t="e">
-        <f>+B2677*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2678" s="56">
+        <v>773.45565722644994</v>
       </c>
       <c r="C2678" s="35">
         <f>+C2677*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46509,12 +46522,11 @@
       </c>
     </row>
     <row r="2679" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2679" s="22">
+      <c r="A2679" s="53">
         <v>46162</v>
       </c>
-      <c r="B2679" s="35" t="e">
-        <f>+B2678*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2679" s="54">
+        <v>774.09633739433002</v>
       </c>
       <c r="C2679" s="35">
         <f>+C2678*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46530,12 +46542,11 @@
       </c>
     </row>
     <row r="2680" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2680" s="22">
+      <c r="A2680" s="55">
         <v>46163</v>
       </c>
-      <c r="B2680" s="35" t="e">
-        <f>+B2679*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2680" s="56">
+        <v>774.73754825983997</v>
       </c>
       <c r="C2680" s="35">
         <f>+C2679*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46551,12 +46562,11 @@
       </c>
     </row>
     <row r="2681" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2681" s="22">
+      <c r="A2681" s="53">
         <v>46164</v>
       </c>
-      <c r="B2681" s="35" t="e">
-        <f>+B2680*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2681" s="54">
+        <v>775.37929026255995</v>
       </c>
       <c r="C2681" s="35">
         <f>+C2680*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46572,12 +46582,11 @@
       </c>
     </row>
     <row r="2682" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2682" s="22">
+      <c r="A2682" s="55">
         <v>46165</v>
       </c>
-      <c r="B2682" s="35" t="e">
-        <f>+B2681*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2682" s="56">
+        <v>776.02156384245995</v>
       </c>
       <c r="C2682" s="35">
         <f>+C2681*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46593,12 +46602,11 @@
       </c>
     </row>
     <row r="2683" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2683" s="22">
+      <c r="A2683" s="53">
         <v>46166</v>
       </c>
-      <c r="B2683" s="35" t="e">
-        <f>+B2682*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2683" s="54">
+        <v>776.66436943986002</v>
       </c>
       <c r="C2683" s="35">
         <f>+C2682*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46614,12 +46622,11 @@
       </c>
     </row>
     <row r="2684" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2684" s="22">
+      <c r="A2684" s="55">
         <v>46167</v>
       </c>
-      <c r="B2684" s="35" t="e">
-        <f>+B2683*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2684" s="56">
+        <v>777.30770749544001</v>
       </c>
       <c r="C2684" s="35">
         <f>+C2683*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46635,12 +46642,11 @@
       </c>
     </row>
     <row r="2685" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2685" s="22">
+      <c r="A2685" s="53">
         <v>46168</v>
       </c>
-      <c r="B2685" s="35" t="e">
-        <f>+B2684*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2685" s="54">
+        <v>777.95157845026995</v>
       </c>
       <c r="C2685" s="35">
         <f>+C2684*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46656,12 +46662,11 @@
       </c>
     </row>
     <row r="2686" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2686" s="22">
+      <c r="A2686" s="55">
         <v>46169</v>
       </c>
-      <c r="B2686" s="35" t="e">
-        <f>+B2685*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2686" s="56">
+        <v>778.59598274576001</v>
       </c>
       <c r="C2686" s="35">
         <f>+C2685*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46677,12 +46682,11 @@
       </c>
     </row>
     <row r="2687" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2687" s="22">
+      <c r="A2687" s="53">
         <v>46170</v>
       </c>
-      <c r="B2687" s="35" t="e">
-        <f>+B2686*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2687" s="54">
+        <v>779.24092082369998</v>
       </c>
       <c r="C2687" s="35">
         <f>+C2686*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46698,12 +46702,11 @@
       </c>
     </row>
     <row r="2688" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2688" s="22">
+      <c r="A2688" s="55">
         <v>46171</v>
       </c>
-      <c r="B2688" s="35" t="e">
-        <f>+B2687*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2688" s="56">
+        <v>779.88639312623002</v>
       </c>
       <c r="C2688" s="35">
         <f>+C2687*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46719,12 +46722,11 @@
       </c>
     </row>
     <row r="2689" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2689" s="22">
+      <c r="A2689" s="53">
         <v>46172</v>
       </c>
-      <c r="B2689" s="35" t="e">
-        <f>+B2688*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2689" s="54">
+        <v>780.53240009587</v>
       </c>
       <c r="C2689" s="35">
         <f>+C2688*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46740,12 +46742,11 @@
       </c>
     </row>
     <row r="2690" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2690" s="22">
+      <c r="A2690" s="55">
         <v>46173</v>
       </c>
-      <c r="B2690" s="35" t="e">
-        <f>+B2689*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2690" s="56">
+        <v>781.17894217550997</v>
       </c>
       <c r="C2690" s="35">
         <f>+C2689*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46761,12 +46762,11 @@
       </c>
     </row>
     <row r="2691" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2691" s="22">
+      <c r="A2691" s="53">
         <v>46174</v>
       </c>
-      <c r="B2691" s="35" t="e">
-        <f>+B2690*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2691" s="54">
+        <v>781.82601980840002</v>
       </c>
       <c r="C2691" s="35">
         <f>+C2690*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46782,12 +46782,11 @@
       </c>
     </row>
     <row r="2692" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2692" s="22">
+      <c r="A2692" s="55">
         <v>46175</v>
       </c>
-      <c r="B2692" s="35" t="e">
-        <f>+B2691*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2692" s="56">
+        <v>782.47363343815005</v>
       </c>
       <c r="C2692" s="35">
         <f>+C2691*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46803,12 +46802,11 @@
       </c>
     </row>
     <row r="2693" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2693" s="22">
+      <c r="A2693" s="53">
         <v>46176</v>
       </c>
-      <c r="B2693" s="35" t="e">
-        <f>+B2692*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2693" s="54">
+        <v>783.12178350875001</v>
       </c>
       <c r="C2693" s="35">
         <f>+C2692*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46824,12 +46822,11 @@
       </c>
     </row>
     <row r="2694" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2694" s="22">
+      <c r="A2694" s="55">
         <v>46177</v>
       </c>
-      <c r="B2694" s="35" t="e">
-        <f>+B2693*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2694" s="56">
+        <v>783.77047046455004</v>
       </c>
       <c r="C2694" s="35">
         <f>+C2693*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46845,12 +46842,11 @@
       </c>
     </row>
     <row r="2695" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2695" s="22">
+      <c r="A2695" s="53">
         <v>46178</v>
       </c>
-      <c r="B2695" s="35" t="e">
-        <f>+B2694*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2695" s="54">
+        <v>784.41969475026997</v>
       </c>
       <c r="C2695" s="35">
         <f>+C2694*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46866,12 +46862,11 @@
       </c>
     </row>
     <row r="2696" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2696" s="22">
+      <c r="A2696" s="55">
         <v>46179</v>
       </c>
-      <c r="B2696" s="35" t="e">
-        <f>+B2695*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2696" s="56">
+        <v>785.06945681100001</v>
       </c>
       <c r="C2696" s="35">
         <f>+C2695*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46887,12 +46882,11 @@
       </c>
     </row>
     <row r="2697" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2697" s="22">
+      <c r="A2697" s="53">
         <v>46180</v>
       </c>
-      <c r="B2697" s="35" t="e">
-        <f>+B2696*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2697" s="54">
+        <v>785.71975709219998</v>
       </c>
       <c r="C2697" s="35">
         <f>+C2696*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46908,12 +46902,11 @@
       </c>
     </row>
     <row r="2698" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2698" s="22">
+      <c r="A2698" s="55">
         <v>46181</v>
       </c>
-      <c r="B2698" s="35" t="e">
-        <f>+B2697*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2698" s="56">
+        <v>786.37059603969999</v>
       </c>
       <c r="C2698" s="35">
         <f>+C2697*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46929,12 +46922,11 @@
       </c>
     </row>
     <row r="2699" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2699" s="22">
+      <c r="A2699" s="53">
         <v>46182</v>
       </c>
-      <c r="B2699" s="35" t="e">
-        <f>+B2698*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2699" s="54">
+        <v>787.02197409968005</v>
       </c>
       <c r="C2699" s="35">
         <f>+C2698*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46950,12 +46942,11 @@
       </c>
     </row>
     <row r="2700" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2700" s="22">
+      <c r="A2700" s="55">
         <v>46183</v>
       </c>
-      <c r="B2700" s="35" t="e">
-        <f>+B2699*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2700" s="56">
+        <v>787.67389171873003</v>
       </c>
       <c r="C2700" s="35">
         <f>+C2699*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46971,12 +46962,11 @@
       </c>
     </row>
     <row r="2701" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2701" s="22">
+      <c r="A2701" s="53">
         <v>46184</v>
       </c>
-      <c r="B2701" s="35" t="e">
-        <f>+B2700*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2701" s="54">
+        <v>788.32634934375994</v>
       </c>
       <c r="C2701" s="35">
         <f>+C2700*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -46992,12 +46982,11 @@
       </c>
     </row>
     <row r="2702" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2702" s="22">
+      <c r="A2702" s="55">
         <v>46185</v>
       </c>
-      <c r="B2702" s="35" t="e">
-        <f>+B2701*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2702" s="56">
+        <v>788.97934742209998</v>
       </c>
       <c r="C2702" s="35">
         <f>+C2701*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -47013,12 +47002,11 @@
       </c>
     </row>
     <row r="2703" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2703" s="22">
+      <c r="A2703" s="53">
         <v>46186</v>
       </c>
-      <c r="B2703" s="35" t="e">
-        <f>+B2702*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2703" s="54">
+        <v>789.63288640140001</v>
       </c>
       <c r="C2703" s="35">
         <f>+C2702*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -47034,12 +47022,11 @@
       </c>
     </row>
     <row r="2704" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2704" s="22">
+      <c r="A2704" s="55">
         <v>46187</v>
       </c>
-      <c r="B2704" s="35" t="e">
-        <f>+B2703*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2704" s="56">
+        <v>790.28696672973001</v>
       </c>
       <c r="C2704" s="35">
         <f>+C2703*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -47055,12 +47042,11 @@
       </c>
     </row>
     <row r="2705" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2705" s="29">
+      <c r="A2705" s="53">
         <v>46188</v>
       </c>
-      <c r="B2705" s="35" t="e">
-        <f>+B2704*((1+#REF!)^(1/#REF!))</f>
-        <v>#REF!</v>
+      <c r="B2705" s="54">
+        <v>790.94158885549996</v>
       </c>
       <c r="C2705" s="35">
         <f>+C2704*((1+INFLA!$B$6)^(1/-_xlfn.DAYS($A$2674,$A$2705)))</f>
@@ -52380,6 +52366,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52395,11 +52386,6 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/ssegura_balanz_com/Documents/Escritorio/curvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80FA7194-CE52-402C-BC78-67D5A55CAA3D}"/>
+  <xr:revisionPtr revIDLastSave="437" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{969DF339-F269-48F0-B534-24C23B970827}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
@@ -168,7 +168,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,6 +263,19 @@
       <sz val="9"/>
       <color rgb="FF003A70"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF003A70"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -393,7 +406,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -519,10 +532,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -535,6 +544,23 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -875,7 +901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3510784-F91E-4B31-AAC1-BAAEF41263FE}">
-  <dimension ref="A1:F2827"/>
+  <dimension ref="A1:H2827"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.21875" style="35" bestFit="1" customWidth="1"/>
@@ -46442,10 +46468,10 @@
       </c>
     </row>
     <row r="2675" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2675" s="53">
+      <c r="A2675" s="51">
         <v>46158</v>
       </c>
-      <c r="B2675" s="54">
+      <c r="B2675" s="52">
         <v>771.53679651802997</v>
       </c>
       <c r="C2675" s="35">
@@ -46462,10 +46488,10 @@
       </c>
     </row>
     <row r="2676" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2676" s="55">
+      <c r="A2676" s="53">
         <v>46159</v>
       </c>
-      <c r="B2676" s="56">
+      <c r="B2676" s="54">
         <v>772.17588722697997</v>
       </c>
       <c r="C2676" s="35">
@@ -46482,10 +46508,10 @@
       </c>
     </row>
     <row r="2677" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2677" s="53">
+      <c r="A2677" s="51">
         <v>46160</v>
       </c>
-      <c r="B2677" s="54">
+      <c r="B2677" s="52">
         <v>772.81550731695995</v>
       </c>
       <c r="C2677" s="35">
@@ -46502,10 +46528,10 @@
       </c>
     </row>
     <row r="2678" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2678" s="55">
+      <c r="A2678" s="53">
         <v>46161</v>
       </c>
-      <c r="B2678" s="56">
+      <c r="B2678" s="54">
         <v>773.45565722644994</v>
       </c>
       <c r="C2678" s="35">
@@ -46522,10 +46548,10 @@
       </c>
     </row>
     <row r="2679" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2679" s="53">
+      <c r="A2679" s="51">
         <v>46162</v>
       </c>
-      <c r="B2679" s="54">
+      <c r="B2679" s="52">
         <v>774.09633739433002</v>
       </c>
       <c r="C2679" s="35">
@@ -46542,10 +46568,10 @@
       </c>
     </row>
     <row r="2680" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2680" s="55">
+      <c r="A2680" s="53">
         <v>46163</v>
       </c>
-      <c r="B2680" s="56">
+      <c r="B2680" s="54">
         <v>774.73754825983997</v>
       </c>
       <c r="C2680" s="35">
@@ -46562,10 +46588,10 @@
       </c>
     </row>
     <row r="2681" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2681" s="53">
+      <c r="A2681" s="51">
         <v>46164</v>
       </c>
-      <c r="B2681" s="54">
+      <c r="B2681" s="52">
         <v>775.37929026255995</v>
       </c>
       <c r="C2681" s="35">
@@ -46582,10 +46608,10 @@
       </c>
     </row>
     <row r="2682" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2682" s="55">
+      <c r="A2682" s="53">
         <v>46165</v>
       </c>
-      <c r="B2682" s="56">
+      <c r="B2682" s="54">
         <v>776.02156384245995</v>
       </c>
       <c r="C2682" s="35">
@@ -46602,10 +46628,10 @@
       </c>
     </row>
     <row r="2683" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2683" s="53">
+      <c r="A2683" s="51">
         <v>46166</v>
       </c>
-      <c r="B2683" s="54">
+      <c r="B2683" s="52">
         <v>776.66436943986002</v>
       </c>
       <c r="C2683" s="35">
@@ -46622,10 +46648,10 @@
       </c>
     </row>
     <row r="2684" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2684" s="55">
+      <c r="A2684" s="53">
         <v>46167</v>
       </c>
-      <c r="B2684" s="56">
+      <c r="B2684" s="54">
         <v>777.30770749544001</v>
       </c>
       <c r="C2684" s="35">
@@ -46642,10 +46668,10 @@
       </c>
     </row>
     <row r="2685" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2685" s="53">
+      <c r="A2685" s="51">
         <v>46168</v>
       </c>
-      <c r="B2685" s="54">
+      <c r="B2685" s="52">
         <v>777.95157845026995</v>
       </c>
       <c r="C2685" s="35">
@@ -46662,10 +46688,10 @@
       </c>
     </row>
     <row r="2686" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2686" s="55">
+      <c r="A2686" s="53">
         <v>46169</v>
       </c>
-      <c r="B2686" s="56">
+      <c r="B2686" s="54">
         <v>778.59598274576001</v>
       </c>
       <c r="C2686" s="35">
@@ -46682,10 +46708,10 @@
       </c>
     </row>
     <row r="2687" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2687" s="53">
+      <c r="A2687" s="51">
         <v>46170</v>
       </c>
-      <c r="B2687" s="54">
+      <c r="B2687" s="52">
         <v>779.24092082369998</v>
       </c>
       <c r="C2687" s="35">
@@ -46702,10 +46728,10 @@
       </c>
     </row>
     <row r="2688" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2688" s="55">
+      <c r="A2688" s="53">
         <v>46171</v>
       </c>
-      <c r="B2688" s="56">
+      <c r="B2688" s="54">
         <v>779.88639312623002</v>
       </c>
       <c r="C2688" s="35">
@@ -46722,10 +46748,10 @@
       </c>
     </row>
     <row r="2689" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2689" s="53">
+      <c r="A2689" s="51">
         <v>46172</v>
       </c>
-      <c r="B2689" s="54">
+      <c r="B2689" s="52">
         <v>780.53240009587</v>
       </c>
       <c r="C2689" s="35">
@@ -46742,10 +46768,10 @@
       </c>
     </row>
     <row r="2690" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2690" s="55">
+      <c r="A2690" s="53">
         <v>46173</v>
       </c>
-      <c r="B2690" s="56">
+      <c r="B2690" s="54">
         <v>781.17894217550997</v>
       </c>
       <c r="C2690" s="35">
@@ -46762,10 +46788,10 @@
       </c>
     </row>
     <row r="2691" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2691" s="53">
+      <c r="A2691" s="51">
         <v>46174</v>
       </c>
-      <c r="B2691" s="54">
+      <c r="B2691" s="52">
         <v>781.82601980840002</v>
       </c>
       <c r="C2691" s="35">
@@ -46782,10 +46808,10 @@
       </c>
     </row>
     <row r="2692" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2692" s="55">
+      <c r="A2692" s="53">
         <v>46175</v>
       </c>
-      <c r="B2692" s="56">
+      <c r="B2692" s="54">
         <v>782.47363343815005</v>
       </c>
       <c r="C2692" s="35">
@@ -46802,10 +46828,10 @@
       </c>
     </row>
     <row r="2693" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2693" s="53">
+      <c r="A2693" s="51">
         <v>46176</v>
       </c>
-      <c r="B2693" s="54">
+      <c r="B2693" s="52">
         <v>783.12178350875001</v>
       </c>
       <c r="C2693" s="35">
@@ -46822,10 +46848,10 @@
       </c>
     </row>
     <row r="2694" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2694" s="55">
+      <c r="A2694" s="53">
         <v>46177</v>
       </c>
-      <c r="B2694" s="56">
+      <c r="B2694" s="54">
         <v>783.77047046455004</v>
       </c>
       <c r="C2694" s="35">
@@ -46842,10 +46868,10 @@
       </c>
     </row>
     <row r="2695" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2695" s="53">
+      <c r="A2695" s="51">
         <v>46178</v>
       </c>
-      <c r="B2695" s="54">
+      <c r="B2695" s="52">
         <v>784.41969475026997</v>
       </c>
       <c r="C2695" s="35">
@@ -46862,10 +46888,10 @@
       </c>
     </row>
     <row r="2696" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2696" s="55">
+      <c r="A2696" s="53">
         <v>46179</v>
       </c>
-      <c r="B2696" s="56">
+      <c r="B2696" s="54">
         <v>785.06945681100001</v>
       </c>
       <c r="C2696" s="35">
@@ -46882,10 +46908,10 @@
       </c>
     </row>
     <row r="2697" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2697" s="53">
+      <c r="A2697" s="51">
         <v>46180</v>
       </c>
-      <c r="B2697" s="54">
+      <c r="B2697" s="52">
         <v>785.71975709219998</v>
       </c>
       <c r="C2697" s="35">
@@ -46902,10 +46928,10 @@
       </c>
     </row>
     <row r="2698" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2698" s="55">
+      <c r="A2698" s="53">
         <v>46181</v>
       </c>
-      <c r="B2698" s="56">
+      <c r="B2698" s="54">
         <v>786.37059603969999</v>
       </c>
       <c r="C2698" s="35">
@@ -46922,10 +46948,10 @@
       </c>
     </row>
     <row r="2699" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2699" s="53">
+      <c r="A2699" s="51">
         <v>46182</v>
       </c>
-      <c r="B2699" s="54">
+      <c r="B2699" s="52">
         <v>787.02197409968005</v>
       </c>
       <c r="C2699" s="35">
@@ -46942,10 +46968,10 @@
       </c>
     </row>
     <row r="2700" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2700" s="55">
+      <c r="A2700" s="53">
         <v>46183</v>
       </c>
-      <c r="B2700" s="56">
+      <c r="B2700" s="54">
         <v>787.67389171873003</v>
       </c>
       <c r="C2700" s="35">
@@ -46962,10 +46988,10 @@
       </c>
     </row>
     <row r="2701" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2701" s="53">
+      <c r="A2701" s="51">
         <v>46184</v>
       </c>
-      <c r="B2701" s="54">
+      <c r="B2701" s="52">
         <v>788.32634934375994</v>
       </c>
       <c r="C2701" s="35">
@@ -46982,10 +47008,10 @@
       </c>
     </row>
     <row r="2702" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2702" s="55">
+      <c r="A2702" s="53">
         <v>46185</v>
       </c>
-      <c r="B2702" s="56">
+      <c r="B2702" s="54">
         <v>788.97934742209998</v>
       </c>
       <c r="C2702" s="35">
@@ -47002,10 +47028,10 @@
       </c>
     </row>
     <row r="2703" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2703" s="53">
+      <c r="A2703" s="51">
         <v>46186</v>
       </c>
-      <c r="B2703" s="54">
+      <c r="B2703" s="52">
         <v>789.63288640140001</v>
       </c>
       <c r="C2703" s="35">
@@ -47022,10 +47048,10 @@
       </c>
     </row>
     <row r="2704" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2704" s="55">
+      <c r="A2704" s="53">
         <v>46187</v>
       </c>
-      <c r="B2704" s="56">
+      <c r="B2704" s="54">
         <v>790.28696672973001</v>
       </c>
       <c r="C2704" s="35">
@@ -47041,11 +47067,11 @@
         <v>790.18112831444716</v>
       </c>
     </row>
-    <row r="2705" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2705" s="53">
+    <row r="2705" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2705" s="51">
         <v>46188</v>
       </c>
-      <c r="B2705" s="54">
+      <c r="B2705" s="52">
         <v>790.94158885549996</v>
       </c>
       <c r="C2705" s="35">
@@ -47061,13 +47087,12 @@
         <v>790.88317170002188</v>
       </c>
     </row>
-    <row r="2706" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2706" s="22">
+    <row r="2706" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2706" s="57">
         <v>46189</v>
       </c>
-      <c r="B2706" s="35" t="e">
-        <f>+B2705*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2706" s="58">
+        <v>791.48970450621005</v>
       </c>
       <c r="C2706" s="35">
         <f>+C2705*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47082,13 +47107,12 @@
         <v>791.50865229766077</v>
       </c>
     </row>
-    <row r="2707" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2707" s="22">
+    <row r="2707" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2707" s="59">
         <v>46190</v>
       </c>
-      <c r="B2707" s="35" t="e">
-        <f>+B2706*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2707" s="60">
+        <v>792.03819999631003</v>
       </c>
       <c r="C2707" s="35">
         <f>+C2706*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47103,13 +47127,12 @@
         <v>792.13462756504612</v>
       </c>
     </row>
-    <row r="2708" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2708" s="22">
+    <row r="2708" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2708" s="57">
         <v>46191</v>
       </c>
-      <c r="B2708" s="35" t="e">
-        <f>+B2707*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2708" s="58">
+        <v>792.58707558901995</v>
       </c>
       <c r="C2708" s="35">
         <f>+C2707*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47124,13 +47147,12 @@
         <v>792.76109789339409</v>
       </c>
     </row>
-    <row r="2709" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2709" s="22">
+    <row r="2709" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2709" s="59">
         <v>46192</v>
       </c>
-      <c r="B2709" s="35" t="e">
-        <f>+B2708*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2709" s="60">
+        <v>793.13633154774004</v>
       </c>
       <c r="C2709" s="35">
         <f>+C2708*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47144,14 +47166,14 @@
         <f>+E2708*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>793.38806367423035</v>
       </c>
-    </row>
-    <row r="2710" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2710" s="22">
+      <c r="H2709" s="61"/>
+    </row>
+    <row r="2710" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2710" s="57">
         <v>46193</v>
       </c>
-      <c r="B2710" s="35" t="e">
-        <f>+B2709*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2710" s="58">
+        <v>793.68596813607996</v>
       </c>
       <c r="C2710" s="35">
         <f>+C2709*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47166,13 +47188,12 @@
         <v>794.01552529939022</v>
       </c>
     </row>
-    <row r="2711" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2711" s="22">
+    <row r="2711" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2711" s="59">
         <v>46194</v>
       </c>
-      <c r="B2711" s="35" t="e">
-        <f>+B2710*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2711" s="60">
+        <v>794.23598561778999</v>
       </c>
       <c r="C2711" s="35">
         <f>+C2710*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47187,13 +47208,12 @@
         <v>794.64348316101882</v>
       </c>
     </row>
-    <row r="2712" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2712" s="22">
+    <row r="2712" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2712" s="57">
         <v>46195</v>
       </c>
-      <c r="B2712" s="35" t="e">
-        <f>+B2711*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2712" s="58">
+        <v>794.78638425684005</v>
       </c>
       <c r="C2712" s="35">
         <f>+C2711*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47208,13 +47228,12 @@
         <v>795.27193765157142</v>
       </c>
     </row>
-    <row r="2713" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2713" s="22">
+    <row r="2713" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2713" s="59">
         <v>46196</v>
       </c>
-      <c r="B2713" s="35" t="e">
-        <f>+B2712*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2713" s="60">
+        <v>795.33716431737002</v>
       </c>
       <c r="C2713" s="35">
         <f>+C2712*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47229,13 +47248,12 @@
         <v>795.90088916381376</v>
       </c>
     </row>
-    <row r="2714" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2714" s="22">
+    <row r="2714" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2714" s="57">
         <v>46197</v>
       </c>
-      <c r="B2714" s="35" t="e">
-        <f>+B2713*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2714" s="58">
+        <v>795.88832606369999</v>
       </c>
       <c r="C2714" s="35">
         <f>+C2713*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47250,13 +47268,12 @@
         <v>796.53033809082206</v>
       </c>
     </row>
-    <row r="2715" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2715" s="22">
+    <row r="2715" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2715" s="59">
         <v>46198</v>
       </c>
-      <c r="B2715" s="35" t="e">
-        <f>+B2714*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2715" s="60">
+        <v>796.43986976033</v>
       </c>
       <c r="C2715" s="35">
         <f>+C2714*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47271,13 +47288,12 @@
         <v>797.16028482598347</v>
       </c>
     </row>
-    <row r="2716" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2716" s="22">
+    <row r="2716" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2716" s="57">
         <v>46199</v>
       </c>
-      <c r="B2716" s="35" t="e">
-        <f>+B2715*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2716" s="58">
+        <v>796.99179567194994</v>
       </c>
       <c r="C2716" s="35">
         <f>+C2715*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47292,13 +47308,12 @@
         <v>797.79072976299631</v>
       </c>
     </row>
-    <row r="2717" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2717" s="22">
+    <row r="2717" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2717" s="59">
         <v>46200</v>
       </c>
-      <c r="B2717" s="35" t="e">
-        <f>+B2716*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2717" s="60">
+        <v>797.54410406343004</v>
       </c>
       <c r="C2717" s="35">
         <f>+C2716*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47313,13 +47328,12 @@
         <v>798.42167329587016</v>
       </c>
     </row>
-    <row r="2718" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2718" s="22">
+    <row r="2718" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2718" s="57">
         <v>46201</v>
       </c>
-      <c r="B2718" s="35" t="e">
-        <f>+B2717*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2718" s="58">
+        <v>798.09679519983001</v>
       </c>
       <c r="C2718" s="35">
         <f>+C2717*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47334,13 +47348,12 @@
         <v>799.05311581892636</v>
       </c>
     </row>
-    <row r="2719" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2719" s="22">
+    <row r="2719" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2719" s="59">
         <v>46202</v>
       </c>
-      <c r="B2719" s="35" t="e">
-        <f>+B2718*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2719" s="60">
+        <v>798.64986934639001</v>
       </c>
       <c r="C2719" s="35">
         <f>+C2718*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47355,13 +47368,12 @@
         <v>799.68505772679794</v>
       </c>
     </row>
-    <row r="2720" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2720" s="22">
+    <row r="2720" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2720" s="57">
         <v>46203</v>
       </c>
-      <c r="B2720" s="35" t="e">
-        <f>+B2719*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2720" s="58">
+        <v>799.20332676852001</v>
       </c>
       <c r="C2720" s="35">
         <f>+C2719*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47377,12 +47389,11 @@
       </c>
     </row>
     <row r="2721" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2721" s="22">
+      <c r="A2721" s="59">
         <v>46204</v>
       </c>
-      <c r="B2721" s="35" t="e">
-        <f>+B2720*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2721" s="60">
+        <v>799.75716773184001</v>
       </c>
       <c r="C2721" s="35">
         <f>+C2720*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47398,12 +47409,11 @@
       </c>
     </row>
     <row r="2722" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2722" s="22">
+      <c r="A2722" s="57">
         <v>46205</v>
       </c>
-      <c r="B2722" s="35" t="e">
-        <f>+B2721*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2722" s="58">
+        <v>800.31139250214005</v>
       </c>
       <c r="C2722" s="35">
         <f>+C2721*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47419,12 +47429,11 @@
       </c>
     </row>
     <row r="2723" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2723" s="22">
+      <c r="A2723" s="59">
         <v>46206</v>
       </c>
-      <c r="B2723" s="35" t="e">
-        <f>+B2722*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2723" s="60">
+        <v>800.86600134539003</v>
       </c>
       <c r="C2723" s="35">
         <f>+C2722*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47440,12 +47449,11 @@
       </c>
     </row>
     <row r="2724" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2724" s="22">
+      <c r="A2724" s="57">
         <v>46207</v>
       </c>
-      <c r="B2724" s="35" t="e">
-        <f>+B2723*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2724" s="58">
+        <v>801.42099452775005</v>
       </c>
       <c r="C2724" s="35">
         <f>+C2723*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47461,12 +47469,11 @@
       </c>
     </row>
     <row r="2725" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2725" s="22">
+      <c r="A2725" s="59">
         <v>46208</v>
       </c>
-      <c r="B2725" s="35" t="e">
-        <f>+B2724*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2725" s="60">
+        <v>801.97637231556996</v>
       </c>
       <c r="C2725" s="35">
         <f>+C2724*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47482,12 +47489,11 @@
       </c>
     </row>
     <row r="2726" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2726" s="22">
+      <c r="A2726" s="57">
         <v>46209</v>
       </c>
-      <c r="B2726" s="35" t="e">
-        <f>+B2725*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2726" s="58">
+        <v>802.53213497537001</v>
       </c>
       <c r="C2726" s="35">
         <f>+C2725*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47503,12 +47509,11 @@
       </c>
     </row>
     <row r="2727" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2727" s="22">
+      <c r="A2727" s="59">
         <v>46210</v>
       </c>
-      <c r="B2727" s="35" t="e">
-        <f>+B2726*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2727" s="60">
+        <v>803.08828277385999</v>
       </c>
       <c r="C2727" s="35">
         <f>+C2726*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47524,12 +47529,11 @@
       </c>
     </row>
     <row r="2728" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2728" s="22">
+      <c r="A2728" s="57">
         <v>46211</v>
       </c>
-      <c r="B2728" s="35" t="e">
-        <f>+B2727*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2728" s="58">
+        <v>803.64481597794997</v>
       </c>
       <c r="C2728" s="35">
         <f>+C2727*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47545,12 +47549,11 @@
       </c>
     </row>
     <row r="2729" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2729" s="22">
+      <c r="A2729" s="59">
         <v>46212</v>
       </c>
-      <c r="B2729" s="35" t="e">
-        <f>+B2728*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2729" s="60">
+        <v>804.20173485471003</v>
       </c>
       <c r="C2729" s="35">
         <f>+C2728*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47566,12 +47569,11 @@
       </c>
     </row>
     <row r="2730" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2730" s="22">
+      <c r="A2730" s="57">
         <v>46213</v>
       </c>
-      <c r="B2730" s="35" t="e">
-        <f>+B2729*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2730" s="58">
+        <v>804.75903967142006</v>
       </c>
       <c r="C2730" s="35">
         <f>+C2729*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47587,12 +47589,11 @@
       </c>
     </row>
     <row r="2731" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2731" s="22">
+      <c r="A2731" s="59">
         <v>46214</v>
       </c>
-      <c r="B2731" s="35" t="e">
-        <f>+B2730*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2731" s="60">
+        <v>805.31673069553005</v>
       </c>
       <c r="C2731" s="35">
         <f>+C2730*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47608,12 +47609,11 @@
       </c>
     </row>
     <row r="2732" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2732" s="22">
+      <c r="A2732" s="57">
         <v>46215</v>
       </c>
-      <c r="B2732" s="35" t="e">
-        <f>+B2731*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2732" s="58">
+        <v>805.87480819466998</v>
       </c>
       <c r="C2732" s="35">
         <f>+C2731*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47629,12 +47629,11 @@
       </c>
     </row>
     <row r="2733" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2733" s="22">
+      <c r="A2733" s="59">
         <v>46216</v>
       </c>
-      <c r="B2733" s="35" t="e">
-        <f>+B2732*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2733" s="60">
+        <v>806.43327243666999</v>
       </c>
       <c r="C2733" s="35">
         <f>+C2732*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47650,12 +47649,11 @@
       </c>
     </row>
     <row r="2734" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2734" s="22">
+      <c r="A2734" s="57">
         <v>46217</v>
       </c>
-      <c r="B2734" s="35" t="e">
-        <f>+B2733*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2734" s="58">
+        <v>806.99212368953999</v>
       </c>
       <c r="C2734" s="35">
         <f>+C2733*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -47671,12 +47669,11 @@
       </c>
     </row>
     <row r="2735" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2735" s="29">
+      <c r="A2735" s="59">
         <v>46218</v>
       </c>
-      <c r="B2735" s="35" t="e">
-        <f>+B2734*(1+#REF!)^(1/#REF!)</f>
-        <v>#REF!</v>
+      <c r="B2735" s="60">
+        <v>807.55136222146996</v>
       </c>
       <c r="C2735" s="35">
         <f>+C2734*((1+INFLA!$B$7)^(1/-_xlfn.DAYS($A$2705,$A$2735)))</f>
@@ -49470,12 +49467,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -49568,12 +49565,12 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
       <c r="H8" s="10">
         <v>45596</v>
       </c>
@@ -49646,12 +49643,12 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
       <c r="H13" s="8">
         <v>45323</v>
       </c>
@@ -49724,12 +49721,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
       <c r="H18" s="10">
         <v>37986</v>
       </c>
@@ -49802,12 +49799,12 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -49848,12 +49845,12 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -49894,12 +49891,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -49940,12 +49937,12 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
@@ -49986,12 +49983,12 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="51" t="s">
+      <c r="A43" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -50032,12 +50029,12 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="51" t="s">
+      <c r="A48" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
@@ -50078,12 +50075,12 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="51" t="s">
+      <c r="A53" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
@@ -50124,12 +50121,12 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="51" t="s">
+      <c r="A58" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="52"/>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
@@ -50171,12 +50168,12 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="51" t="s">
+      <c r="A63" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="52"/>
-      <c r="C63" s="52"/>
-      <c r="D63" s="52"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="56"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
@@ -50252,12 +50249,12 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="51" t="s">
+      <c r="A70" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="52"/>
-      <c r="C70" s="52"/>
-      <c r="D70" s="52"/>
+      <c r="B70" s="56"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
@@ -50401,12 +50398,12 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="51" t="s">
+      <c r="A81" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
+      <c r="B81" s="56"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
@@ -50643,12 +50640,12 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="51" t="s">
+      <c r="A98" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B98" s="52"/>
-      <c r="C98" s="52"/>
-      <c r="D98" s="52"/>
+      <c r="B98" s="56"/>
+      <c r="C98" s="56"/>
+      <c r="D98" s="56"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
@@ -50962,12 +50959,12 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="51" t="s">
+      <c r="A119" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B119" s="52"/>
-      <c r="C119" s="52"/>
-      <c r="D119" s="52"/>
+      <c r="B119" s="56"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="56"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
@@ -51447,12 +51444,12 @@
       <c r="A150" s="6"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="51" t="s">
+      <c r="A151" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B151" s="52"/>
-      <c r="C151" s="52"/>
-      <c r="D151" s="52"/>
+      <c r="B151" s="56"/>
+      <c r="C151" s="56"/>
+      <c r="D151" s="56"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
@@ -52111,12 +52108,12 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="51" t="s">
+      <c r="A196" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B196" s="52"/>
-      <c r="C196" s="52"/>
-      <c r="D196" s="52"/>
+      <c r="B196" s="56"/>
+      <c r="C196" s="56"/>
+      <c r="D196" s="56"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
@@ -52283,12 +52280,12 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="51" t="s">
+      <c r="A209" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B209" s="52"/>
-      <c r="C209" s="52"/>
-      <c r="D209" s="52"/>
+      <c r="B209" s="56"/>
+      <c r="C209" s="56"/>
+      <c r="D209" s="56"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
@@ -52366,11 +52363,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52386,6 +52378,11 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/ssegura_balanz_com/Documents/Escritorio/curvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="437" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{969DF339-F269-48F0-B534-24C23B970827}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3053C65D-AAB7-46E8-A552-BC0E2F017765}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
+    <workbookView xWindow="-17595" yWindow="-7605" windowWidth="17280" windowHeight="15585" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
   <sheets>
     <sheet name="CER" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="36">
   <si>
     <t>Payment Date</t>
   </si>
@@ -148,12 +148,6 @@
     <t>Cer Rem</t>
   </si>
   <si>
-    <t>ene</t>
-  </si>
-  <si>
-    <t>dic</t>
-  </si>
-  <si>
     <t>Cer Comafi</t>
   </si>
 </sst>
@@ -161,14 +155,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +271,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF003A70"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="10">
@@ -406,7 +406,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -544,10 +544,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -561,6 +557,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -922,7 +935,7 @@
         <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -44156,7 +44169,7 @@
         <v>679.50609999999995</v>
       </c>
     </row>
-    <row r="2545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2545" s="1">
         <v>46028</v>
       </c>
@@ -44173,7 +44186,7 @@
         <v>680.04750000000001</v>
       </c>
     </row>
-    <row r="2546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2546" s="2">
         <v>46029</v>
       </c>
@@ -44190,7 +44203,7 @@
         <v>680.58939999999996</v>
       </c>
     </row>
-    <row r="2547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2547" s="1">
         <v>46030</v>
       </c>
@@ -44207,7 +44220,7 @@
         <v>681.1318</v>
       </c>
     </row>
-    <row r="2548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2548" s="2">
         <v>46031</v>
       </c>
@@ -44224,7 +44237,7 @@
         <v>681.67449999999997</v>
       </c>
     </row>
-    <row r="2549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2549" s="1">
         <v>46032</v>
       </c>
@@ -44241,7 +44254,7 @@
         <v>682.21770000000004</v>
       </c>
     </row>
-    <row r="2550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2550" s="2">
         <v>46033</v>
       </c>
@@ -44258,7 +44271,7 @@
         <v>682.76130000000001</v>
       </c>
     </row>
-    <row r="2551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2551" s="1">
         <v>46034</v>
       </c>
@@ -44275,7 +44288,7 @@
         <v>683.30539999999996</v>
       </c>
     </row>
-    <row r="2552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2552" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2552" s="2">
         <v>46035</v>
       </c>
@@ -44292,7 +44305,7 @@
         <v>683.84990000000005</v>
       </c>
     </row>
-    <row r="2553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2553" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2553" s="1">
         <v>46036</v>
       </c>
@@ -44309,7 +44322,7 @@
         <v>684.39480000000003</v>
       </c>
     </row>
-    <row r="2554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2554" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2554" s="2">
         <v>46037</v>
       </c>
@@ -44325,8 +44338,12 @@
       <c r="E2554" s="36">
         <v>684.9402</v>
       </c>
-    </row>
-    <row r="2555" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2554" s="66">
+        <f>+B2554/B2523</f>
+        <v>1.0250000636004468</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2555" s="1">
         <v>46038</v>
       </c>
@@ -44343,7 +44360,7 @@
         <v>685.55060000000003</v>
       </c>
     </row>
-    <row r="2556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2556" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2556" s="2">
         <v>46039</v>
       </c>
@@ -44360,7 +44377,7 @@
         <v>686.16160000000002</v>
       </c>
     </row>
-    <row r="2557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2557" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2557" s="1">
         <v>46040</v>
       </c>
@@ -44377,7 +44394,7 @@
         <v>686.7731</v>
       </c>
     </row>
-    <row r="2558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2558" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2558" s="2">
         <v>46041</v>
       </c>
@@ -44394,7 +44411,7 @@
         <v>687.38520000000005</v>
       </c>
     </row>
-    <row r="2559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2559" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2559" s="1">
         <v>46042</v>
       </c>
@@ -44411,7 +44428,7 @@
         <v>687.99779999999998</v>
       </c>
     </row>
-    <row r="2560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2560" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2560" s="2">
         <v>46043</v>
       </c>
@@ -44852,8 +44869,9 @@
       <c r="E2585" s="37">
         <v>704.11850000000004</v>
       </c>
-      <c r="F2585" t="s">
-        <v>36</v>
+      <c r="F2585" s="66">
+        <f>+B2585/B2554</f>
+        <v>1.0279999626244745</v>
       </c>
     </row>
     <row r="2586" spans="1:6" x14ac:dyDescent="0.3">
@@ -45331,8 +45349,9 @@
       <c r="E2613" s="39">
         <v>724.53790000000004</v>
       </c>
-      <c r="F2613" t="s">
-        <v>35</v>
+      <c r="F2613" s="66">
+        <f>+B2613/B2585</f>
+        <v>1.0289999481621346</v>
       </c>
     </row>
     <row r="2614" spans="1:6" x14ac:dyDescent="0.3">
@@ -45844,6 +45863,7 @@
       <c r="E2643" s="43">
         <v>744.86233904134997</v>
       </c>
+      <c r="F2643" s="66"/>
     </row>
     <row r="2644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2644" s="29">
@@ -45861,6 +45881,10 @@
       <c r="E2644" s="42">
         <v>745.54955005023999</v>
       </c>
+      <c r="F2644" s="66">
+        <f>+B2644/B2613</f>
+        <v>1.0290000703210143</v>
+      </c>
     </row>
     <row r="2645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2645" s="47">
@@ -46427,7 +46451,7 @@
         <v>767.7931442509298</v>
       </c>
     </row>
-    <row r="2673" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2673" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2673" s="47">
         <v>46156</v>
       </c>
@@ -46447,7 +46471,7 @@
         <v>768.59971629661186</v>
       </c>
     </row>
-    <row r="2674" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2674" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2674" s="49">
         <v>46157</v>
       </c>
@@ -46466,8 +46490,12 @@
         <f>+E2673*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>769.40713565184569</v>
       </c>
-    </row>
-    <row r="2675" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2674" s="66">
+        <f>+B2674/B2644</f>
+        <v>1.0340000000000025</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2675" s="51">
         <v>46158</v>
       </c>
@@ -46487,7 +46515,7 @@
         <v>770.09072220060386</v>
       </c>
     </row>
-    <row r="2676" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2676" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2676" s="53">
         <v>46159</v>
       </c>
@@ -46507,7 +46535,7 @@
         <v>770.77491608785419</v>
       </c>
     </row>
-    <row r="2677" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2677" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2677" s="51">
         <v>46160</v>
       </c>
@@ -46527,7 +46555,7 @@
         <v>771.45971785319193</v>
       </c>
     </row>
-    <row r="2678" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2678" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2678" s="53">
         <v>46161</v>
       </c>
@@ -46547,7 +46575,7 @@
         <v>772.14512803669174</v>
       </c>
     </row>
-    <row r="2679" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2679" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2679" s="51">
         <v>46162</v>
       </c>
@@ -46567,7 +46595,7 @@
         <v>772.83114717890817</v>
       </c>
     </row>
-    <row r="2680" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2680" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2680" s="53">
         <v>46163</v>
       </c>
@@ -46587,7 +46615,7 @@
         <v>773.51777582087584</v>
       </c>
     </row>
-    <row r="2681" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2681" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2681" s="51">
         <v>46164</v>
       </c>
@@ -46607,7 +46635,7 @@
         <v>774.20501450411018</v>
       </c>
     </row>
-    <row r="2682" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2682" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2682" s="53">
         <v>46165</v>
       </c>
@@ -46627,7 +46655,7 @@
         <v>774.89286377060773</v>
       </c>
     </row>
-    <row r="2683" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2683" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2683" s="51">
         <v>46166</v>
       </c>
@@ -46647,7 +46675,7 @@
         <v>775.58132416284661</v>
       </c>
     </row>
-    <row r="2684" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2684" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2684" s="53">
         <v>46167</v>
       </c>
@@ -46667,7 +46695,7 @@
         <v>776.27039622378686</v>
       </c>
     </row>
-    <row r="2685" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2685" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2685" s="51">
         <v>46168</v>
       </c>
@@ -46687,7 +46715,7 @@
         <v>776.960080496871</v>
       </c>
     </row>
-    <row r="2686" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2686" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2686" s="53">
         <v>46169</v>
       </c>
@@ -46707,7 +46735,7 @@
         <v>777.65037752602416</v>
       </c>
     </row>
-    <row r="2687" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2687" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2687" s="51">
         <v>46170</v>
       </c>
@@ -46727,7 +46755,7 @@
         <v>778.34128785565497</v>
       </c>
     </row>
-    <row r="2688" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2688" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2688" s="53">
         <v>46171</v>
       </c>
@@ -47086,12 +47114,16 @@
         <f>+E2704*((1+INFLA!$D$6)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>790.88317170002188</v>
       </c>
+      <c r="F2705">
+        <f>+B2705/B2674</f>
+        <v>1.0259999999999991</v>
+      </c>
     </row>
     <row r="2706" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2706" s="57">
+      <c r="A2706" s="55">
         <v>46189</v>
       </c>
-      <c r="B2706" s="58">
+      <c r="B2706" s="56">
         <v>791.48970450621005</v>
       </c>
       <c r="C2706" s="35">
@@ -47108,10 +47140,10 @@
       </c>
     </row>
     <row r="2707" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2707" s="59">
+      <c r="A2707" s="57">
         <v>46190</v>
       </c>
-      <c r="B2707" s="60">
+      <c r="B2707" s="58">
         <v>792.03819999631003</v>
       </c>
       <c r="C2707" s="35">
@@ -47128,10 +47160,10 @@
       </c>
     </row>
     <row r="2708" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2708" s="57">
+      <c r="A2708" s="55">
         <v>46191</v>
       </c>
-      <c r="B2708" s="58">
+      <c r="B2708" s="56">
         <v>792.58707558901995</v>
       </c>
       <c r="C2708" s="35">
@@ -47148,10 +47180,10 @@
       </c>
     </row>
     <row r="2709" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2709" s="59">
+      <c r="A2709" s="57">
         <v>46192</v>
       </c>
-      <c r="B2709" s="60">
+      <c r="B2709" s="58">
         <v>793.13633154774004</v>
       </c>
       <c r="C2709" s="35">
@@ -47166,13 +47198,13 @@
         <f>+E2708*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>793.38806367423035</v>
       </c>
-      <c r="H2709" s="61"/>
+      <c r="H2709" s="59"/>
     </row>
     <row r="2710" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2710" s="57">
+      <c r="A2710" s="55">
         <v>46193</v>
       </c>
-      <c r="B2710" s="58">
+      <c r="B2710" s="56">
         <v>793.68596813607996</v>
       </c>
       <c r="C2710" s="35">
@@ -47189,10 +47221,10 @@
       </c>
     </row>
     <row r="2711" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2711" s="59">
+      <c r="A2711" s="57">
         <v>46194</v>
       </c>
-      <c r="B2711" s="60">
+      <c r="B2711" s="58">
         <v>794.23598561778999</v>
       </c>
       <c r="C2711" s="35">
@@ -47209,10 +47241,10 @@
       </c>
     </row>
     <row r="2712" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2712" s="57">
+      <c r="A2712" s="55">
         <v>46195</v>
       </c>
-      <c r="B2712" s="58">
+      <c r="B2712" s="56">
         <v>794.78638425684005</v>
       </c>
       <c r="C2712" s="35">
@@ -47229,10 +47261,10 @@
       </c>
     </row>
     <row r="2713" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2713" s="59">
+      <c r="A2713" s="57">
         <v>46196</v>
       </c>
-      <c r="B2713" s="60">
+      <c r="B2713" s="58">
         <v>795.33716431737002</v>
       </c>
       <c r="C2713" s="35">
@@ -47249,10 +47281,10 @@
       </c>
     </row>
     <row r="2714" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2714" s="57">
+      <c r="A2714" s="55">
         <v>46197</v>
       </c>
-      <c r="B2714" s="58">
+      <c r="B2714" s="56">
         <v>795.88832606369999</v>
       </c>
       <c r="C2714" s="35">
@@ -47269,10 +47301,10 @@
       </c>
     </row>
     <row r="2715" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2715" s="59">
+      <c r="A2715" s="57">
         <v>46198</v>
       </c>
-      <c r="B2715" s="60">
+      <c r="B2715" s="58">
         <v>796.43986976033</v>
       </c>
       <c r="C2715" s="35">
@@ -47289,10 +47321,10 @@
       </c>
     </row>
     <row r="2716" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2716" s="57">
+      <c r="A2716" s="55">
         <v>46199</v>
       </c>
-      <c r="B2716" s="58">
+      <c r="B2716" s="56">
         <v>796.99179567194994</v>
       </c>
       <c r="C2716" s="35">
@@ -47309,10 +47341,10 @@
       </c>
     </row>
     <row r="2717" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2717" s="59">
+      <c r="A2717" s="57">
         <v>46200</v>
       </c>
-      <c r="B2717" s="60">
+      <c r="B2717" s="58">
         <v>797.54410406343004</v>
       </c>
       <c r="C2717" s="35">
@@ -47329,10 +47361,10 @@
       </c>
     </row>
     <row r="2718" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2718" s="57">
+      <c r="A2718" s="55">
         <v>46201</v>
       </c>
-      <c r="B2718" s="58">
+      <c r="B2718" s="56">
         <v>798.09679519983001</v>
       </c>
       <c r="C2718" s="35">
@@ -47349,10 +47381,10 @@
       </c>
     </row>
     <row r="2719" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2719" s="59">
+      <c r="A2719" s="57">
         <v>46202</v>
       </c>
-      <c r="B2719" s="60">
+      <c r="B2719" s="58">
         <v>798.64986934639001</v>
       </c>
       <c r="C2719" s="35">
@@ -47369,10 +47401,10 @@
       </c>
     </row>
     <row r="2720" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2720" s="57">
+      <c r="A2720" s="55">
         <v>46203</v>
       </c>
-      <c r="B2720" s="58">
+      <c r="B2720" s="56">
         <v>799.20332676852001</v>
       </c>
       <c r="C2720" s="35">
@@ -47388,11 +47420,11 @@
         <v>800.31749941443013</v>
       </c>
     </row>
-    <row r="2721" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2721" s="59">
+    <row r="2721" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2721" s="57">
         <v>46204</v>
       </c>
-      <c r="B2721" s="60">
+      <c r="B2721" s="58">
         <v>799.75716773184001</v>
       </c>
       <c r="C2721" s="35">
@@ -47408,11 +47440,11 @@
         <v>800.95044127708036</v>
       </c>
     </row>
-    <row r="2722" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2722" s="57">
+    <row r="2722" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2722" s="55">
         <v>46205</v>
       </c>
-      <c r="B2722" s="58">
+      <c r="B2722" s="56">
         <v>800.31139250214005</v>
       </c>
       <c r="C2722" s="35">
@@ -47428,11 +47460,11 @@
         <v>801.5838837103189</v>
       </c>
     </row>
-    <row r="2723" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2723" s="59">
+    <row r="2723" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2723" s="57">
         <v>46206</v>
       </c>
-      <c r="B2723" s="60">
+      <c r="B2723" s="58">
         <v>800.86600134539003</v>
       </c>
       <c r="C2723" s="35">
@@ -47448,11 +47480,11 @@
         <v>802.21782711002868</v>
       </c>
     </row>
-    <row r="2724" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2724" s="57">
+    <row r="2724" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2724" s="55">
         <v>46207</v>
       </c>
-      <c r="B2724" s="58">
+      <c r="B2724" s="56">
         <v>801.42099452775005</v>
       </c>
       <c r="C2724" s="35">
@@ -47468,11 +47500,11 @@
         <v>802.85227187240582</v>
       </c>
     </row>
-    <row r="2725" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2725" s="59">
+    <row r="2725" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2725" s="57">
         <v>46208</v>
       </c>
-      <c r="B2725" s="60">
+      <c r="B2725" s="58">
         <v>801.97637231556996</v>
       </c>
       <c r="C2725" s="35">
@@ -47488,11 +47520,11 @@
         <v>803.48721839395978</v>
       </c>
     </row>
-    <row r="2726" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2726" s="57">
+    <row r="2726" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2726" s="55">
         <v>46209</v>
       </c>
-      <c r="B2726" s="58">
+      <c r="B2726" s="56">
         <v>802.53213497537001</v>
       </c>
       <c r="C2726" s="35">
@@ -47508,11 +47540,11 @@
         <v>804.12266707151343</v>
       </c>
     </row>
-    <row r="2727" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2727" s="59">
+    <row r="2727" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2727" s="57">
         <v>46210</v>
       </c>
-      <c r="B2727" s="60">
+      <c r="B2727" s="58">
         <v>803.08828277385999</v>
       </c>
       <c r="C2727" s="35">
@@ -47528,11 +47560,11 @@
         <v>804.75861830220367</v>
       </c>
     </row>
-    <row r="2728" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2728" s="57">
+    <row r="2728" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2728" s="55">
         <v>46211</v>
       </c>
-      <c r="B2728" s="58">
+      <c r="B2728" s="56">
         <v>803.64481597794997</v>
       </c>
       <c r="C2728" s="35">
@@ -47548,11 +47580,11 @@
         <v>805.39507248348139</v>
       </c>
     </row>
-    <row r="2729" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2729" s="59">
+    <row r="2729" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2729" s="57">
         <v>46212</v>
       </c>
-      <c r="B2729" s="60">
+      <c r="B2729" s="58">
         <v>804.20173485471003</v>
       </c>
       <c r="C2729" s="35">
@@ -47568,11 +47600,11 @@
         <v>806.03203001311181</v>
       </c>
     </row>
-    <row r="2730" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2730" s="57">
+    <row r="2730" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2730" s="55">
         <v>46213</v>
       </c>
-      <c r="B2730" s="58">
+      <c r="B2730" s="56">
         <v>804.75903967142006</v>
       </c>
       <c r="C2730" s="35">
@@ -47588,11 +47620,11 @@
         <v>806.66949128917486</v>
       </c>
     </row>
-    <row r="2731" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2731" s="59">
+    <row r="2731" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2731" s="57">
         <v>46214</v>
       </c>
-      <c r="B2731" s="60">
+      <c r="B2731" s="58">
         <v>805.31673069553005</v>
       </c>
       <c r="C2731" s="35">
@@ -47608,11 +47640,11 @@
         <v>807.30745671006503</v>
       </c>
     </row>
-    <row r="2732" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2732" s="57">
+    <row r="2732" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2732" s="55">
         <v>46215</v>
       </c>
-      <c r="B2732" s="58">
+      <c r="B2732" s="56">
         <v>805.87480819466998</v>
       </c>
       <c r="C2732" s="35">
@@ -47628,11 +47660,11 @@
         <v>807.94592667449217</v>
       </c>
     </row>
-    <row r="2733" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2733" s="59">
+    <row r="2733" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2733" s="57">
         <v>46216</v>
       </c>
-      <c r="B2733" s="60">
+      <c r="B2733" s="58">
         <v>806.43327243666999</v>
       </c>
       <c r="C2733" s="35">
@@ -47648,11 +47680,11 @@
         <v>808.58490158148129</v>
       </c>
     </row>
-    <row r="2734" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2734" s="57">
+    <row r="2734" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2734" s="55">
         <v>46217</v>
       </c>
-      <c r="B2734" s="58">
+      <c r="B2734" s="56">
         <v>806.99212368953999</v>
       </c>
       <c r="C2734" s="35">
@@ -47668,11 +47700,11 @@
         <v>809.22438183037298</v>
       </c>
     </row>
-    <row r="2735" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2735" s="59">
+    <row r="2735" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2735" s="57">
         <v>46218</v>
       </c>
-      <c r="B2735" s="60">
+      <c r="B2735" s="58">
         <v>807.55136222146996</v>
       </c>
       <c r="C2735" s="35">
@@ -47687,10 +47719,17 @@
         <f>+E2734*((1+INFLA!$D$7)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>809.86436782082365</v>
       </c>
-    </row>
-    <row r="2736" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2736" s="22">
+      <c r="F2735">
+        <f>+B2735/B2705</f>
+        <v>1.0210000000000057</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2736" s="62">
         <v>46219</v>
+      </c>
+      <c r="B2736" s="63">
+        <v>808.04181862256996</v>
       </c>
       <c r="C2736" s="35">
         <f>+C2735*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47706,8 +47745,11 @@
       </c>
     </row>
     <row r="2737" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2737" s="22">
+      <c r="A2737" s="64">
         <v>46220</v>
+      </c>
+      <c r="B2737" s="65">
+        <v>808.53257289634996</v>
       </c>
       <c r="C2737" s="35">
         <f>+C2736*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47723,8 +47765,11 @@
       </c>
     </row>
     <row r="2738" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2738" s="22">
+      <c r="A2738" s="62">
         <v>46221</v>
+      </c>
+      <c r="B2738" s="63">
+        <v>809.02362522370004</v>
       </c>
       <c r="C2738" s="35">
         <f>+C2737*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47740,8 +47785,11 @@
       </c>
     </row>
     <row r="2739" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2739" s="22">
+      <c r="A2739" s="64">
         <v>46222</v>
+      </c>
+      <c r="B2739" s="65">
+        <v>809.51497578566</v>
       </c>
       <c r="C2739" s="35">
         <f>+C2738*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47757,8 +47805,11 @@
       </c>
     </row>
     <row r="2740" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2740" s="22">
+      <c r="A2740" s="62">
         <v>46223</v>
+      </c>
+      <c r="B2740" s="63">
+        <v>810.00662476334003</v>
       </c>
       <c r="C2740" s="35">
         <f>+C2739*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47774,8 +47825,11 @@
       </c>
     </row>
     <row r="2741" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2741" s="22">
+      <c r="A2741" s="64">
         <v>46224</v>
+      </c>
+      <c r="B2741" s="65">
+        <v>810.49857233800003</v>
       </c>
       <c r="C2741" s="35">
         <f>+C2740*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47791,8 +47845,11 @@
       </c>
     </row>
     <row r="2742" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2742" s="22">
+      <c r="A2742" s="62">
         <v>46225</v>
+      </c>
+      <c r="B2742" s="63">
+        <v>810.99081869096995</v>
       </c>
       <c r="C2742" s="35">
         <f>+C2741*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47808,8 +47865,11 @@
       </c>
     </row>
     <row r="2743" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2743" s="22">
+      <c r="A2743" s="64">
         <v>46226</v>
+      </c>
+      <c r="B2743" s="65">
+        <v>811.48336400370999</v>
       </c>
       <c r="C2743" s="35">
         <f>+C2742*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47825,8 +47885,11 @@
       </c>
     </row>
     <row r="2744" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2744" s="22">
+      <c r="A2744" s="62">
         <v>46227</v>
+      </c>
+      <c r="B2744" s="63">
+        <v>811.97620845781</v>
       </c>
       <c r="C2744" s="35">
         <f>+C2743*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47842,8 +47905,11 @@
       </c>
     </row>
     <row r="2745" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2745" s="22">
+      <c r="A2745" s="64">
         <v>46228</v>
+      </c>
+      <c r="B2745" s="65">
+        <v>812.46935223492005</v>
       </c>
       <c r="C2745" s="35">
         <f>+C2744*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47859,8 +47925,11 @@
       </c>
     </row>
     <row r="2746" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2746" s="22">
+      <c r="A2746" s="62">
         <v>46229</v>
+      </c>
+      <c r="B2746" s="63">
+        <v>812.96279551685996</v>
       </c>
       <c r="C2746" s="35">
         <f>+C2745*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47876,8 +47945,11 @@
       </c>
     </row>
     <row r="2747" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2747" s="22">
+      <c r="A2747" s="64">
         <v>46230</v>
+      </c>
+      <c r="B2747" s="65">
+        <v>813.45653848551001</v>
       </c>
       <c r="C2747" s="35">
         <f>+C2746*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47893,8 +47965,11 @@
       </c>
     </row>
     <row r="2748" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2748" s="22">
+      <c r="A2748" s="62">
         <v>46231</v>
+      </c>
+      <c r="B2748" s="63">
+        <v>813.95058132289</v>
       </c>
       <c r="C2748" s="35">
         <f>+C2747*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47910,8 +47985,11 @@
       </c>
     </row>
     <row r="2749" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2749" s="22">
+      <c r="A2749" s="64">
         <v>46232</v>
+      </c>
+      <c r="B2749" s="65">
+        <v>814.44492421112</v>
       </c>
       <c r="C2749" s="35">
         <f>+C2748*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47927,8 +48005,11 @@
       </c>
     </row>
     <row r="2750" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2750" s="22">
+      <c r="A2750" s="62">
         <v>46233</v>
+      </c>
+      <c r="B2750" s="63">
+        <v>814.93956733241998</v>
       </c>
       <c r="C2750" s="35">
         <f>+C2749*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47944,8 +48025,11 @@
       </c>
     </row>
     <row r="2751" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2751" s="22">
+      <c r="A2751" s="64">
         <v>46234</v>
+      </c>
+      <c r="B2751" s="65">
+        <v>815.43451086916002</v>
       </c>
       <c r="C2751" s="35">
         <f>+C2750*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47961,8 +48045,11 @@
       </c>
     </row>
     <row r="2752" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2752" s="22">
+      <c r="A2752" s="62">
         <v>46235</v>
+      </c>
+      <c r="B2752" s="63">
+        <v>815.92975500376997</v>
       </c>
       <c r="C2752" s="35">
         <f>+C2751*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47977,9 +48064,12 @@
         <v>819.91305038513792</v>
       </c>
     </row>
-    <row r="2753" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2753" s="22">
+    <row r="2753" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2753" s="64">
         <v>46236</v>
+      </c>
+      <c r="B2753" s="65">
+        <v>816.42529991881997</v>
       </c>
       <c r="C2753" s="35">
         <f>+C2752*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -47994,9 +48084,12 @@
         <v>820.5080171853856</v>
       </c>
     </row>
-    <row r="2754" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2754" s="22">
+    <row r="2754" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2754" s="62">
         <v>46237</v>
+      </c>
+      <c r="B2754" s="63">
+        <v>816.92114579699</v>
       </c>
       <c r="C2754" s="35">
         <f>+C2753*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48011,9 +48104,12 @@
         <v>821.10341572103891</v>
       </c>
     </row>
-    <row r="2755" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2755" s="22">
+    <row r="2755" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2755" s="64">
         <v>46238</v>
+      </c>
+      <c r="B2755" s="65">
+        <v>817.41729282106996</v>
       </c>
       <c r="C2755" s="35">
         <f>+C2754*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48028,9 +48124,12 @@
         <v>821.69924630538503</v>
       </c>
     </row>
-    <row r="2756" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2756" s="22">
+    <row r="2756" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2756" s="62">
         <v>46239</v>
+      </c>
+      <c r="B2756" s="63">
+        <v>817.91374117394002</v>
       </c>
       <c r="C2756" s="35">
         <f>+C2755*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48045,9 +48144,12 @@
         <v>822.29550925193837</v>
       </c>
     </row>
-    <row r="2757" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2757" s="22">
+    <row r="2757" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2757" s="64">
         <v>46240</v>
+      </c>
+      <c r="B2757" s="65">
+        <v>818.41049103862997</v>
       </c>
       <c r="C2757" s="35">
         <f>+C2756*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48062,9 +48164,12 @@
         <v>822.89220487444106</v>
       </c>
     </row>
-    <row r="2758" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2758" s="22">
+    <row r="2758" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2758" s="62">
         <v>46241</v>
+      </c>
+      <c r="B2758" s="63">
+        <v>818.90754259823996</v>
       </c>
       <c r="C2758" s="35">
         <f>+C2757*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48079,9 +48184,12 @@
         <v>823.48933348686273</v>
       </c>
     </row>
-    <row r="2759" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2759" s="22">
+    <row r="2759" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2759" s="64">
         <v>46242</v>
+      </c>
+      <c r="B2759" s="65">
+        <v>819.40489603601998</v>
       </c>
       <c r="C2759" s="35">
         <f>+C2758*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48096,9 +48204,12 @@
         <v>824.08689540340083</v>
       </c>
     </row>
-    <row r="2760" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2760" s="22">
+    <row r="2760" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2760" s="62">
         <v>46243</v>
+      </c>
+      <c r="B2760" s="63">
+        <v>819.90255153528994</v>
       </c>
       <c r="C2760" s="35">
         <f>+C2759*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48113,9 +48224,12 @@
         <v>824.68489093848086</v>
       </c>
     </row>
-    <row r="2761" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2761" s="22">
+    <row r="2761" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2761" s="64">
         <v>46244</v>
+      </c>
+      <c r="B2761" s="65">
+        <v>820.40050927951995</v>
       </c>
       <c r="C2761" s="35">
         <f>+C2760*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48130,9 +48244,12 @@
         <v>825.2833204067565</v>
       </c>
     </row>
-    <row r="2762" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2762" s="22">
+    <row r="2762" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2762" s="62">
         <v>46245</v>
+      </c>
+      <c r="B2762" s="63">
+        <v>820.89876945228002</v>
       </c>
       <c r="C2762" s="35">
         <f>+C2761*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48147,9 +48264,12 @@
         <v>825.88218412310971</v>
       </c>
     </row>
-    <row r="2763" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2763" s="22">
+    <row r="2763" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2763" s="64">
         <v>46246</v>
+      </c>
+      <c r="B2763" s="65">
+        <v>821.39733223721998</v>
       </c>
       <c r="C2763" s="35">
         <f>+C2762*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48164,9 +48284,12 @@
         <v>826.48148240265095</v>
       </c>
     </row>
-    <row r="2764" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2764" s="22">
+    <row r="2764" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2764" s="62">
         <v>46247</v>
+      </c>
+      <c r="B2764" s="63">
+        <v>821.89619781814997</v>
       </c>
       <c r="C2764" s="35">
         <f>+C2763*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48181,9 +48304,12 @@
         <v>827.08121556071944</v>
       </c>
     </row>
-    <row r="2765" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2765" s="22">
+    <row r="2765" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2765" s="64">
         <v>46248</v>
+      </c>
+      <c r="B2765" s="65">
+        <v>822.39536637897004</v>
       </c>
       <c r="C2765" s="35">
         <f>+C2764*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48198,9 +48324,12 @@
         <v>827.68138391288312</v>
       </c>
     </row>
-    <row r="2766" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2766" s="29">
+    <row r="2766" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2766" s="62">
         <v>46249</v>
+      </c>
+      <c r="B2766" s="63">
+        <v>822.89483810367994</v>
       </c>
       <c r="C2766" s="35">
         <f>+C2765*((1+INFLA!$B$8)^(1/-_xlfn.DAYS($A$2735,$A$2766)))</f>
@@ -48214,8 +48343,12 @@
         <f>+E2765*((1+INFLA!$D$8)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>828.28198777493878</v>
       </c>
-    </row>
-    <row r="2767" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2766">
+        <f>+B2766/B2735</f>
+        <v>1.0190000000000026</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2767" s="22">
         <v>46250</v>
       </c>
@@ -48232,7 +48365,7 @@
         <v>828.86363227995025</v>
       </c>
     </row>
-    <row r="2768" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2768" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2768" s="22">
         <v>46251</v>
       </c>
@@ -49467,12 +49600,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -49565,12 +49698,12 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
       <c r="H8" s="10">
         <v>45596</v>
       </c>
@@ -49643,12 +49776,12 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
       <c r="H13" s="8">
         <v>45323</v>
       </c>
@@ -49721,12 +49854,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
       <c r="H18" s="10">
         <v>37986</v>
       </c>
@@ -49799,12 +49932,12 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -49845,12 +49978,12 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -49891,12 +50024,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -49937,12 +50070,12 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
@@ -49983,12 +50116,12 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
+      <c r="B43" s="61"/>
+      <c r="C43" s="61"/>
+      <c r="D43" s="61"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -50029,12 +50162,12 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="55" t="s">
+      <c r="A48" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="56"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
+      <c r="B48" s="61"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
@@ -50075,12 +50208,12 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="55" t="s">
+      <c r="A53" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
+      <c r="B53" s="61"/>
+      <c r="C53" s="61"/>
+      <c r="D53" s="61"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
@@ -50121,12 +50254,12 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="55" t="s">
+      <c r="A58" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
+      <c r="B58" s="61"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
@@ -50168,12 +50301,12 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="55" t="s">
+      <c r="A63" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
+      <c r="B63" s="61"/>
+      <c r="C63" s="61"/>
+      <c r="D63" s="61"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
@@ -50249,12 +50382,12 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="55" t="s">
+      <c r="A70" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="56"/>
-      <c r="C70" s="56"/>
-      <c r="D70" s="56"/>
+      <c r="B70" s="61"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="61"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
@@ -50398,12 +50531,12 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="55" t="s">
+      <c r="A81" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="56"/>
-      <c r="C81" s="56"/>
-      <c r="D81" s="56"/>
+      <c r="B81" s="61"/>
+      <c r="C81" s="61"/>
+      <c r="D81" s="61"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
@@ -50640,12 +50773,12 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="55" t="s">
+      <c r="A98" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="56"/>
-      <c r="D98" s="56"/>
+      <c r="B98" s="61"/>
+      <c r="C98" s="61"/>
+      <c r="D98" s="61"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
@@ -50959,12 +51092,12 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="55" t="s">
+      <c r="A119" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B119" s="56"/>
-      <c r="C119" s="56"/>
-      <c r="D119" s="56"/>
+      <c r="B119" s="61"/>
+      <c r="C119" s="61"/>
+      <c r="D119" s="61"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
@@ -51444,12 +51577,12 @@
       <c r="A150" s="6"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="55" t="s">
+      <c r="A151" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B151" s="56"/>
-      <c r="C151" s="56"/>
-      <c r="D151" s="56"/>
+      <c r="B151" s="61"/>
+      <c r="C151" s="61"/>
+      <c r="D151" s="61"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
@@ -52108,12 +52241,12 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="55" t="s">
+      <c r="A196" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B196" s="56"/>
-      <c r="C196" s="56"/>
-      <c r="D196" s="56"/>
+      <c r="B196" s="61"/>
+      <c r="C196" s="61"/>
+      <c r="D196" s="61"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
@@ -52280,12 +52413,12 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="55" t="s">
+      <c r="A209" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B209" s="56"/>
-      <c r="C209" s="56"/>
-      <c r="D209" s="56"/>
+      <c r="B209" s="61"/>
+      <c r="C209" s="61"/>
+      <c r="D209" s="61"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
@@ -52363,6 +52496,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52378,11 +52516,6 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CER.xlsx
+++ b/CER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/ssegura_balanz_com/Documents/Escritorio/curvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3053C65D-AAB7-46E8-A552-BC0E2F017765}"/>
+  <xr:revisionPtr revIDLastSave="457" documentId="8_{1398FB6E-3DD2-4A10-AF87-7BA56C4A53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90CBB6FF-5278-45CF-BFC3-3BC8B50AE8BA}"/>
   <bookViews>
-    <workbookView xWindow="-17595" yWindow="-7605" windowWidth="17280" windowHeight="15585" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
+    <workbookView xWindow="-18315" yWindow="-7605" windowWidth="17280" windowHeight="15585" xr2:uid="{C1B1CFF9-A46C-48B2-B4C6-114803BA4979}"/>
   </bookViews>
   <sheets>
     <sheet name="CER" sheetId="2" r:id="rId1"/>
@@ -161,9 +161,9 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +271,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF003A70"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <sz val="9"/>
@@ -406,7 +411,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -557,10 +562,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -573,7 +574,23 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -44338,7 +44355,7 @@
       <c r="E2554" s="36">
         <v>684.9402</v>
       </c>
-      <c r="F2554" s="66">
+      <c r="F2554" s="64">
         <f>+B2554/B2523</f>
         <v>1.0250000636004468</v>
       </c>
@@ -44869,7 +44886,7 @@
       <c r="E2585" s="37">
         <v>704.11850000000004</v>
       </c>
-      <c r="F2585" s="66">
+      <c r="F2585" s="64">
         <f>+B2585/B2554</f>
         <v>1.0279999626244745</v>
       </c>
@@ -45349,7 +45366,7 @@
       <c r="E2613" s="39">
         <v>724.53790000000004</v>
       </c>
-      <c r="F2613" s="66">
+      <c r="F2613" s="64">
         <f>+B2613/B2585</f>
         <v>1.0289999481621346</v>
       </c>
@@ -45863,7 +45880,7 @@
       <c r="E2643" s="43">
         <v>744.86233904134997</v>
       </c>
-      <c r="F2643" s="66"/>
+      <c r="F2643" s="64"/>
     </row>
     <row r="2644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2644" s="29">
@@ -45881,7 +45898,7 @@
       <c r="E2644" s="42">
         <v>745.54955005023999</v>
       </c>
-      <c r="F2644" s="66">
+      <c r="F2644" s="64">
         <f>+B2644/B2613</f>
         <v>1.0290000703210143</v>
       </c>
@@ -46490,7 +46507,7 @@
         <f>+E2673*((1+INFLA!$D$5)^(1/-_xlfn.DAYS(CER!$A$2644,CER!$A$2674)))</f>
         <v>769.40713565184569</v>
       </c>
-      <c r="F2674" s="66">
+      <c r="F2674" s="64">
         <f>+B2674/B2644</f>
         <v>1.0340000000000025</v>
       </c>
@@ -47725,10 +47742,10 @@
       </c>
     </row>
     <row r="2736" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2736" s="62">
+      <c r="A2736" s="60">
         <v>46219</v>
       </c>
-      <c r="B2736" s="63">
+      <c r="B2736" s="61">
         <v>808.04181862256996</v>
       </c>
       <c r="C2736" s="35">
@@ -47745,10 +47762,10 @@
       </c>
     </row>
     <row r="2737" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2737" s="64">
+      <c r="A2737" s="62">
         <v>46220</v>
       </c>
-      <c r="B2737" s="65">
+      <c r="B2737" s="63">
         <v>808.53257289634996</v>
       </c>
       <c r="C2737" s="35">
@@ -47765,10 +47782,10 @@
       </c>
     </row>
     <row r="2738" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2738" s="62">
+      <c r="A2738" s="60">
         <v>46221</v>
       </c>
-      <c r="B2738" s="63">
+      <c r="B2738" s="61">
         <v>809.02362522370004</v>
       </c>
       <c r="C2738" s="35">
@@ -47785,10 +47802,10 @@
       </c>
     </row>
     <row r="2739" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2739" s="64">
+      <c r="A2739" s="62">
         <v>46222</v>
       </c>
-      <c r="B2739" s="65">
+      <c r="B2739" s="63">
         <v>809.51497578566</v>
       </c>
       <c r="C2739" s="35">
@@ -47805,10 +47822,10 @@
       </c>
     </row>
     <row r="2740" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2740" s="62">
+      <c r="A2740" s="60">
         <v>46223</v>
       </c>
-      <c r="B2740" s="63">
+      <c r="B2740" s="61">
         <v>810.00662476334003</v>
       </c>
       <c r="C2740" s="35">
@@ -47825,10 +47842,10 @@
       </c>
     </row>
     <row r="2741" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2741" s="64">
+      <c r="A2741" s="62">
         <v>46224</v>
       </c>
-      <c r="B2741" s="65">
+      <c r="B2741" s="63">
         <v>810.49857233800003</v>
       </c>
       <c r="C2741" s="35">
@@ -47845,10 +47862,10 @@
       </c>
     </row>
     <row r="2742" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2742" s="62">
+      <c r="A2742" s="60">
         <v>46225</v>
       </c>
-      <c r="B2742" s="63">
+      <c r="B2742" s="61">
         <v>810.99081869096995</v>
       </c>
       <c r="C2742" s="35">
@@ -47865,10 +47882,10 @@
       </c>
     </row>
     <row r="2743" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2743" s="64">
+      <c r="A2743" s="62">
         <v>46226</v>
       </c>
-      <c r="B2743" s="65">
+      <c r="B2743" s="63">
         <v>811.48336400370999</v>
       </c>
       <c r="C2743" s="35">
@@ -47885,10 +47902,10 @@
       </c>
     </row>
     <row r="2744" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2744" s="62">
+      <c r="A2744" s="60">
         <v>46227</v>
       </c>
-      <c r="B2744" s="63">
+      <c r="B2744" s="61">
         <v>811.97620845781</v>
       </c>
       <c r="C2744" s="35">
@@ -47905,10 +47922,10 @@
       </c>
     </row>
     <row r="2745" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2745" s="64">
+      <c r="A2745" s="62">
         <v>46228</v>
       </c>
-      <c r="B2745" s="65">
+      <c r="B2745" s="63">
         <v>812.46935223492005</v>
       </c>
       <c r="C2745" s="35">
@@ -47925,10 +47942,10 @@
       </c>
     </row>
     <row r="2746" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2746" s="62">
+      <c r="A2746" s="60">
         <v>46229</v>
       </c>
-      <c r="B2746" s="63">
+      <c r="B2746" s="61">
         <v>812.96279551685996</v>
       </c>
       <c r="C2746" s="35">
@@ -47945,10 +47962,10 @@
       </c>
     </row>
     <row r="2747" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2747" s="64">
+      <c r="A2747" s="62">
         <v>46230</v>
       </c>
-      <c r="B2747" s="65">
+      <c r="B2747" s="63">
         <v>813.45653848551001</v>
       </c>
       <c r="C2747" s="35">
@@ -47965,10 +47982,10 @@
       </c>
     </row>
     <row r="2748" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2748" s="62">
+      <c r="A2748" s="60">
         <v>46231</v>
       </c>
-      <c r="B2748" s="63">
+      <c r="B2748" s="61">
         <v>813.95058132289</v>
       </c>
       <c r="C2748" s="35">
@@ -47985,10 +48002,10 @@
       </c>
     </row>
     <row r="2749" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2749" s="64">
+      <c r="A2749" s="62">
         <v>46232</v>
       </c>
-      <c r="B2749" s="65">
+      <c r="B2749" s="63">
         <v>814.44492421112</v>
       </c>
       <c r="C2749" s="35">
@@ -48005,10 +48022,10 @@
       </c>
     </row>
     <row r="2750" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2750" s="62">
+      <c r="A2750" s="60">
         <v>46233</v>
       </c>
-      <c r="B2750" s="63">
+      <c r="B2750" s="61">
         <v>814.93956733241998</v>
       </c>
       <c r="C2750" s="35">
@@ -48025,10 +48042,10 @@
       </c>
     </row>
     <row r="2751" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2751" s="64">
+      <c r="A2751" s="62">
         <v>46234</v>
       </c>
-      <c r="B2751" s="65">
+      <c r="B2751" s="63">
         <v>815.43451086916002</v>
       </c>
       <c r="C2751" s="35">
@@ -48045,10 +48062,10 @@
       </c>
     </row>
     <row r="2752" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2752" s="62">
+      <c r="A2752" s="60">
         <v>46235</v>
       </c>
-      <c r="B2752" s="63">
+      <c r="B2752" s="61">
         <v>815.92975500376997</v>
       </c>
       <c r="C2752" s="35">
@@ -48065,10 +48082,10 @@
       </c>
     </row>
     <row r="2753" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2753" s="64">
+      <c r="A2753" s="62">
         <v>46236</v>
       </c>
-      <c r="B2753" s="65">
+      <c r="B2753" s="63">
         <v>816.42529991881997</v>
       </c>
       <c r="C2753" s="35">
@@ -48085,10 +48102,10 @@
       </c>
     </row>
     <row r="2754" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2754" s="62">
+      <c r="A2754" s="60">
         <v>46237</v>
       </c>
-      <c r="B2754" s="63">
+      <c r="B2754" s="61">
         <v>816.92114579699</v>
       </c>
       <c r="C2754" s="35">
@@ -48105,10 +48122,10 @@
       </c>
     </row>
     <row r="2755" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2755" s="64">
+      <c r="A2755" s="62">
         <v>46238</v>
       </c>
-      <c r="B2755" s="65">
+      <c r="B2755" s="63">
         <v>817.41729282106996</v>
       </c>
       <c r="C2755" s="35">
@@ -48125,10 +48142,10 @@
       </c>
     </row>
     <row r="2756" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2756" s="62">
+      <c r="A2756" s="60">
         <v>46239</v>
       </c>
-      <c r="B2756" s="63">
+      <c r="B2756" s="61">
         <v>817.91374117394002</v>
       </c>
       <c r="C2756" s="35">
@@ -48145,10 +48162,10 @@
       </c>
     </row>
     <row r="2757" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2757" s="64">
+      <c r="A2757" s="62">
         <v>46240</v>
       </c>
-      <c r="B2757" s="65">
+      <c r="B2757" s="63">
         <v>818.41049103862997</v>
       </c>
       <c r="C2757" s="35">
@@ -48165,10 +48182,10 @@
       </c>
     </row>
     <row r="2758" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2758" s="62">
+      <c r="A2758" s="60">
         <v>46241</v>
       </c>
-      <c r="B2758" s="63">
+      <c r="B2758" s="61">
         <v>818.90754259823996</v>
       </c>
       <c r="C2758" s="35">
@@ -48185,10 +48202,10 @@
       </c>
     </row>
     <row r="2759" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2759" s="64">
+      <c r="A2759" s="62">
         <v>46242</v>
       </c>
-      <c r="B2759" s="65">
+      <c r="B2759" s="63">
         <v>819.40489603601998</v>
       </c>
       <c r="C2759" s="35">
@@ -48205,10 +48222,10 @@
       </c>
     </row>
     <row r="2760" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2760" s="62">
+      <c r="A2760" s="60">
         <v>46243</v>
       </c>
-      <c r="B2760" s="63">
+      <c r="B2760" s="61">
         <v>819.90255153528994</v>
       </c>
       <c r="C2760" s="35">
@@ -48225,10 +48242,10 @@
       </c>
     </row>
     <row r="2761" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2761" s="64">
+      <c r="A2761" s="62">
         <v>46244</v>
       </c>
-      <c r="B2761" s="65">
+      <c r="B2761" s="63">
         <v>820.40050927951995</v>
       </c>
       <c r="C2761" s="35">
@@ -48245,10 +48262,10 @@
       </c>
     </row>
     <row r="2762" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2762" s="62">
+      <c r="A2762" s="60">
         <v>46245</v>
       </c>
-      <c r="B2762" s="63">
+      <c r="B2762" s="61">
         <v>820.89876945228002</v>
       </c>
       <c r="C2762" s="35">
@@ -48265,10 +48282,10 @@
       </c>
     </row>
     <row r="2763" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2763" s="64">
+      <c r="A2763" s="62">
         <v>46246</v>
       </c>
-      <c r="B2763" s="65">
+      <c r="B2763" s="63">
         <v>821.39733223721998</v>
       </c>
       <c r="C2763" s="35">
@@ -48285,10 +48302,10 @@
       </c>
     </row>
     <row r="2764" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2764" s="62">
+      <c r="A2764" s="60">
         <v>46247</v>
       </c>
-      <c r="B2764" s="63">
+      <c r="B2764" s="61">
         <v>821.89619781814997</v>
       </c>
       <c r="C2764" s="35">
@@ -48305,10 +48322,10 @@
       </c>
     </row>
     <row r="2765" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2765" s="64">
+      <c r="A2765" s="62">
         <v>46248</v>
       </c>
-      <c r="B2765" s="65">
+      <c r="B2765" s="63">
         <v>822.39536637897004</v>
       </c>
       <c r="C2765" s="35">
@@ -48325,10 +48342,10 @@
       </c>
     </row>
     <row r="2766" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2766" s="62">
+      <c r="A2766" s="60">
         <v>46249</v>
       </c>
-      <c r="B2766" s="63">
+      <c r="B2766" s="61">
         <v>822.89483810367994</v>
       </c>
       <c r="C2766" s="35">
@@ -48349,8 +48366,11 @@
       </c>
     </row>
     <row r="2767" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2767" s="22">
+      <c r="A2767" s="67">
         <v>46250</v>
+      </c>
+      <c r="B2767" s="68">
+        <v>823.44669546089995</v>
       </c>
       <c r="C2767" s="35">
         <f>+C2766*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48366,8 +48386,11 @@
       </c>
     </row>
     <row r="2768" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2768" s="22">
+      <c r="A2768" s="69">
         <v>46251</v>
+      </c>
+      <c r="B2768" s="70">
+        <v>823.99892290980995</v>
       </c>
       <c r="C2768" s="35">
         <f>+C2767*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48381,10 +48404,17 @@
         <f>+E2767*((1+INFLA!$D$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
         <v>829.44568523321391</v>
       </c>
+      <c r="F2768">
+        <f>1.016*1.018*1.016*1.017*1.018*1.018*1.02*F2766*F2735*F2705*F2674*F2644</f>
+        <v>1.2830249582822857</v>
+      </c>
     </row>
     <row r="2769" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2769" s="22">
+      <c r="A2769" s="67">
         <v>46252</v>
+      </c>
+      <c r="B2769" s="68">
+        <v>824.55152069860003</v>
       </c>
       <c r="C2769" s="35">
         <f>+C2768*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48400,8 +48430,11 @@
       </c>
     </row>
     <row r="2770" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2770" s="22">
+      <c r="A2770" s="69">
         <v>46253</v>
+      </c>
+      <c r="B2770" s="70">
+        <v>825.10448907565001</v>
       </c>
       <c r="C2770" s="35">
         <f>+C2769*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48417,8 +48450,11 @@
       </c>
     </row>
     <row r="2771" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2771" s="22">
+      <c r="A2771" s="67">
         <v>46254</v>
+      </c>
+      <c r="B2771" s="68">
+        <v>825.65782828946999</v>
       </c>
       <c r="C2771" s="35">
         <f>+C2770*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48434,8 +48470,11 @@
       </c>
     </row>
     <row r="2772" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2772" s="22">
+      <c r="A2772" s="69">
         <v>46255</v>
+      </c>
+      <c r="B2772" s="70">
+        <v>826.21153858876005</v>
       </c>
       <c r="C2772" s="35">
         <f>+C2771*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48451,8 +48490,11 @@
       </c>
     </row>
     <row r="2773" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2773" s="22">
+      <c r="A2773" s="67">
         <v>46256</v>
+      </c>
+      <c r="B2773" s="68">
+        <v>826.76562022236999</v>
       </c>
       <c r="C2773" s="35">
         <f>+C2772*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48468,8 +48510,11 @@
       </c>
     </row>
     <row r="2774" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2774" s="22">
+      <c r="A2774" s="69">
         <v>46257</v>
+      </c>
+      <c r="B2774" s="70">
+        <v>827.32007343934004</v>
       </c>
       <c r="C2774" s="35">
         <f>+C2773*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48485,8 +48530,11 @@
       </c>
     </row>
     <row r="2775" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2775" s="22">
+      <c r="A2775" s="67">
         <v>46258</v>
+      </c>
+      <c r="B2775" s="68">
+        <v>827.87489848887003</v>
       </c>
       <c r="C2775" s="35">
         <f>+C2774*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48502,8 +48550,11 @@
       </c>
     </row>
     <row r="2776" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2776" s="22">
+      <c r="A2776" s="69">
         <v>46259</v>
+      </c>
+      <c r="B2776" s="70">
+        <v>828.43009562029999</v>
       </c>
       <c r="C2776" s="35">
         <f>+C2775*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48519,8 +48570,11 @@
       </c>
     </row>
     <row r="2777" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2777" s="22">
+      <c r="A2777" s="67">
         <v>46260</v>
+      </c>
+      <c r="B2777" s="68">
+        <v>828.98566508318004</v>
       </c>
       <c r="C2777" s="35">
         <f>+C2776*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48536,8 +48590,11 @@
       </c>
     </row>
     <row r="2778" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2778" s="22">
+      <c r="A2778" s="69">
         <v>46261</v>
+      </c>
+      <c r="B2778" s="70">
+        <v>829.5416071272</v>
       </c>
       <c r="C2778" s="35">
         <f>+C2777*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48553,8 +48610,11 @@
       </c>
     </row>
     <row r="2779" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2779" s="22">
+      <c r="A2779" s="67">
         <v>46262</v>
+      </c>
+      <c r="B2779" s="68">
+        <v>830.09792200222</v>
       </c>
       <c r="C2779" s="35">
         <f>+C2778*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48570,8 +48630,11 @@
       </c>
     </row>
     <row r="2780" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2780" s="22">
+      <c r="A2780" s="69">
         <v>46263</v>
+      </c>
+      <c r="B2780" s="70">
+        <v>830.65460995827004</v>
       </c>
       <c r="C2780" s="35">
         <f>+C2779*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48587,8 +48650,11 @@
       </c>
     </row>
     <row r="2781" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2781" s="22">
+      <c r="A2781" s="67">
         <v>46264</v>
+      </c>
+      <c r="B2781" s="68">
+        <v>831.21167124555996</v>
       </c>
       <c r="C2781" s="35">
         <f>+C2780*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48604,8 +48670,11 @@
       </c>
     </row>
     <row r="2782" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2782" s="22">
+      <c r="A2782" s="69">
         <v>46265</v>
+      </c>
+      <c r="B2782" s="70">
+        <v>831.76910611443998</v>
       </c>
       <c r="C2782" s="35">
         <f>+C2781*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48621,8 +48690,11 @@
       </c>
     </row>
     <row r="2783" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2783" s="22">
+      <c r="A2783" s="67">
         <v>46266</v>
+      </c>
+      <c r="B2783" s="68">
+        <v>832.32691481545999</v>
       </c>
       <c r="C2783" s="35">
         <f>+C2782*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48638,8 +48710,11 @@
       </c>
     </row>
     <row r="2784" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2784" s="22">
+      <c r="A2784" s="69">
         <v>46267</v>
+      </c>
+      <c r="B2784" s="70">
+        <v>832.88509759932003</v>
       </c>
       <c r="C2784" s="35">
         <f>+C2783*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48655,8 +48730,11 @@
       </c>
     </row>
     <row r="2785" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2785" s="22">
+      <c r="A2785" s="67">
         <v>46268</v>
+      </c>
+      <c r="B2785" s="68">
+        <v>833.44365471688002</v>
       </c>
       <c r="C2785" s="35">
         <f>+C2784*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48672,8 +48750,11 @@
       </c>
     </row>
     <row r="2786" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2786" s="22">
+      <c r="A2786" s="69">
         <v>46269</v>
+      </c>
+      <c r="B2786" s="70">
+        <v>834.00258641919004</v>
       </c>
       <c r="C2786" s="35">
         <f>+C2785*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48689,8 +48770,11 @@
       </c>
     </row>
     <row r="2787" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2787" s="22">
+      <c r="A2787" s="67">
         <v>46270</v>
+      </c>
+      <c r="B2787" s="68">
+        <v>834.56189295746003</v>
       </c>
       <c r="C2787" s="35">
         <f>+C2786*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48706,8 +48790,11 @@
       </c>
     </row>
     <row r="2788" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2788" s="22">
+      <c r="A2788" s="69">
         <v>46271</v>
+      </c>
+      <c r="B2788" s="70">
+        <v>835.12157458305001</v>
       </c>
       <c r="C2788" s="35">
         <f>+C2787*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48723,8 +48810,11 @@
       </c>
     </row>
     <row r="2789" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2789" s="22">
+      <c r="A2789" s="67">
         <v>46272</v>
+      </c>
+      <c r="B2789" s="68">
+        <v>835.68163154752006</v>
       </c>
       <c r="C2789" s="35">
         <f>+C2788*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48740,8 +48830,11 @@
       </c>
     </row>
     <row r="2790" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2790" s="22">
+      <c r="A2790" s="69">
         <v>46273</v>
+      </c>
+      <c r="B2790" s="70">
+        <v>836.24206410258</v>
       </c>
       <c r="C2790" s="35">
         <f>+C2789*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48757,8 +48850,11 @@
       </c>
     </row>
     <row r="2791" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2791" s="22">
+      <c r="A2791" s="67">
         <v>46274</v>
+      </c>
+      <c r="B2791" s="68">
+        <v>836.80287250010997</v>
       </c>
       <c r="C2791" s="35">
         <f>+C2790*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48774,8 +48870,11 @@
       </c>
     </row>
     <row r="2792" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2792" s="22">
+      <c r="A2792" s="69">
         <v>46275</v>
+      </c>
+      <c r="B2792" s="70">
+        <v>837.36405699216004</v>
       </c>
       <c r="C2792" s="35">
         <f>+C2791*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48791,8 +48890,11 @@
       </c>
     </row>
     <row r="2793" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2793" s="22">
+      <c r="A2793" s="67">
         <v>46276</v>
+      </c>
+      <c r="B2793" s="68">
+        <v>837.92561783095005</v>
       </c>
       <c r="C2793" s="35">
         <f>+C2792*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48808,8 +48910,11 @@
       </c>
     </row>
     <row r="2794" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2794" s="22">
+      <c r="A2794" s="69">
         <v>46277</v>
+      </c>
+      <c r="B2794" s="70">
+        <v>838.48755526886998</v>
       </c>
       <c r="C2794" s="35">
         <f>+C2793*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48825,8 +48930,11 @@
       </c>
     </row>
     <row r="2795" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2795" s="22">
+      <c r="A2795" s="67">
         <v>46278</v>
+      </c>
+      <c r="B2795" s="68">
+        <v>839.04986955848005</v>
       </c>
       <c r="C2795" s="35">
         <f>+C2794*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48842,8 +48950,11 @@
       </c>
     </row>
     <row r="2796" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2796" s="22">
+      <c r="A2796" s="69">
         <v>46279</v>
+      </c>
+      <c r="B2796" s="70">
+        <v>839.61256095250997</v>
       </c>
       <c r="C2796" s="35">
         <f>+C2795*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -48859,8 +48970,11 @@
       </c>
     </row>
     <row r="2797" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2797" s="29">
+      <c r="A2797" s="67">
         <v>46280</v>
+      </c>
+      <c r="B2797" s="68">
+        <v>840.17562970384995</v>
       </c>
       <c r="C2797" s="35">
         <f>+C2796*((1+INFLA!$B$9)^(1/-_xlfn.DAYS($A$2766,$A$2797)))</f>
@@ -49600,12 +49714,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -49698,12 +49812,12 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
       <c r="H8" s="10">
         <v>45596</v>
       </c>
@@ -49776,12 +49890,12 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
       <c r="H13" s="8">
         <v>45323</v>
       </c>
@@ -49854,12 +49968,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
       <c r="H18" s="10">
         <v>37986</v>
       </c>
@@ -49932,12 +50046,12 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -49978,12 +50092,12 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="60" t="s">
+      <c r="A28" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -50024,12 +50138,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -50070,12 +50184,12 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
@@ -50116,12 +50230,12 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="60" t="s">
+      <c r="A43" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="61"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -50162,12 +50276,12 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="60" t="s">
+      <c r="A48" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="61"/>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
@@ -50208,12 +50322,12 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="60" t="s">
+      <c r="A53" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
-      <c r="D53" s="61"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
@@ -50254,12 +50368,12 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="60" t="s">
+      <c r="A58" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
@@ -50301,12 +50415,12 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="60" t="s">
+      <c r="A63" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="61"/>
-      <c r="C63" s="61"/>
-      <c r="D63" s="61"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="66"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
@@ -50382,12 +50496,12 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="60" t="s">
+      <c r="A70" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="61"/>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="66"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
@@ -50531,12 +50645,12 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="60" t="s">
+      <c r="A81" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
+      <c r="B81" s="66"/>
+      <c r="C81" s="66"/>
+      <c r="D81" s="66"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
@@ -50773,12 +50887,12 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="60" t="s">
+      <c r="A98" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
+      <c r="B98" s="66"/>
+      <c r="C98" s="66"/>
+      <c r="D98" s="66"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
@@ -51092,12 +51206,12 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="60" t="s">
+      <c r="A119" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B119" s="61"/>
-      <c r="C119" s="61"/>
-      <c r="D119" s="61"/>
+      <c r="B119" s="66"/>
+      <c r="C119" s="66"/>
+      <c r="D119" s="66"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
@@ -51577,12 +51691,12 @@
       <c r="A150" s="6"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="60" t="s">
+      <c r="A151" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B151" s="61"/>
-      <c r="C151" s="61"/>
-      <c r="D151" s="61"/>
+      <c r="B151" s="66"/>
+      <c r="C151" s="66"/>
+      <c r="D151" s="66"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
@@ -52241,12 +52355,12 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="60" t="s">
+      <c r="A196" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B196" s="61"/>
-      <c r="C196" s="61"/>
-      <c r="D196" s="61"/>
+      <c r="B196" s="66"/>
+      <c r="C196" s="66"/>
+      <c r="D196" s="66"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
@@ -52413,12 +52527,12 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="60" t="s">
+      <c r="A209" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B209" s="61"/>
-      <c r="C209" s="61"/>
-      <c r="D209" s="61"/>
+      <c r="B209" s="66"/>
+      <c r="C209" s="66"/>
+      <c r="D209" s="66"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
@@ -52496,11 +52610,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A13:D13"/>
@@ -52516,6 +52625,11 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A209:D209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
